--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,414 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44828</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44737</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44555</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44464</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44373</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44282</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1524400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1827600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3866400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1822500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1913700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2322900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5390200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2489300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2016800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2093800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4525500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1825000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1393700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1486200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2274100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1032100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>998000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1163000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2254900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1015100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>988200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1212700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1294400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>993900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>966100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>846100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>859600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1228200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1463200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3108000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1464100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1556200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1872700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4408400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2011000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1645200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1766200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3817700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1538500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1206700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1245200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1901900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>864800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>840800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>975800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1914000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>860900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>850500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1054000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1128800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>863000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>836900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>911900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>725400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>737300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E10" s="3">
         <v>364400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>758400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>358400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>357500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>450200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>981800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>478400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>371600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>327600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>707800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>286600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>187000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>241000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>372200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>167300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>157200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>187200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>341000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>154200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>137700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>158700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>165600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>130900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>129200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>144700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>269000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>120700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>122300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1096,8 +1108,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1188,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1372,8 +1391,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1464,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1660300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3511200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1660800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1745100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2085800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4845600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2230300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1821800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1925700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4151100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1687500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1305500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1379600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2123100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>973400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>946300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1092600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2132300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>966700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>942700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1155700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1233800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>949600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>924600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>812300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>824300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E18" s="3">
         <v>167300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>355200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>161700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>168600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>237100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>544600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>259000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>195000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>168100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>374400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>137500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>106600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>151000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>58700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>51700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>70400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>122600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>48400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>45500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>57000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>60600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>44300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>41500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>52300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>87700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>33800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,91 +1745,92 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E20" s="3">
         <v>9400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>100</v>
@@ -1805,100 +1838,106 @@
       <c r="AF20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E21" s="3">
         <v>209300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>431600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>198500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>208000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>263700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>590600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>283900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>223400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>192400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>422500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>161900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>110700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>126800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>185500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>73100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>71000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>88100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>157100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>66400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>60400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>73100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>75700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>58900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>55500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>66300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>113800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>46400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>48200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1906,46 +1945,46 @@
         <v>3200</v>
       </c>
       <c r="E22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F22" s="3">
         <v>6400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3300</v>
       </c>
       <c r="K22" s="3">
         <v>3300</v>
       </c>
       <c r="L22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3800</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1900</v>
       </c>
       <c r="S22" s="3">
         <v>1900</v>
@@ -1954,227 +1993,236 @@
         <v>1900</v>
       </c>
       <c r="U22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V22" s="3">
         <v>4900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E23" s="3">
         <v>173500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>362100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>164500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>173000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>230700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>531100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>254100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>193100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>163400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>369900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>136000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>88100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>105700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>147200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>53900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>51600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>69000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>120100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>47600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>55300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>58600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>43200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>40300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>50900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>84800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>32400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>34100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E24" s="3">
         <v>39300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>85700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>130100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>37600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>90300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>28900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E26" s="3">
         <v>134200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>276400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>125600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>131900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>172100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>401000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>193100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>147000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>125700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>279600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>104300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>64800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>78900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>110300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>40600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>38700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>52600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>91100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>42100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>45100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>43500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>34700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>56200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E27" s="3">
         <v>127300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>263700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>120600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>127100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>160400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>377700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>182900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>133400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>117100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>267800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>100200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>61200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>75000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>103700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>39100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>50600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>87800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>40300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>43000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>40800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>33000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>53700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2585,8 +2645,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2603,11 +2663,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>8000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2615,11 +2675,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2633,8 +2693,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,91 +2883,94 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>-100</v>
@@ -2909,100 +2978,106 @@
       <c r="AF32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E33" s="3">
         <v>127300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>263700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>120600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>127100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>160400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>377700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>182900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>133400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>117100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>267800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>100200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>61200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>75000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>103700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>39100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>50600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>87800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>34700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>40300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>43000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>30500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>33000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>53700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E35" s="3">
         <v>127300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>263700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>120600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>127100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>160400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>377700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>182900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>133400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>117100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>267800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>100200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>61200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>75000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>103700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>39100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>50600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>87800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>34700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>40300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>43000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>30500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>33000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>53700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44828</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44737</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44555</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44464</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44373</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44282</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,560 +3435,579 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1118300</v>
+      </c>
+      <c r="E41" s="3">
         <v>957100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>702100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>423300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>559400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>449100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>138100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>286700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>138600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>436500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>346200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>32100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>168300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>64500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>27300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>25300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>22000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>31000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>34100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E42" s="3">
         <v>37100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>37500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>35500</v>
       </c>
       <c r="J42" s="3">
         <v>35500</v>
       </c>
       <c r="K42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="L42" s="3">
         <v>36500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>24300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>19200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>17800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>14800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>15800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>582400</v>
+      </c>
+      <c r="E43" s="3">
         <v>725700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>819300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>814800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>657500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>915000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1066000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1102100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>748200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>801900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>984800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>811500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>480500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>587200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>527300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>469200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>382000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>483000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>489600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>456600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>364500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>469200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>497000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>432800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>335000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>422500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>398500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>368800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>293700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>727800</v>
+      </c>
+      <c r="E44" s="3">
         <v>744700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>821200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>960300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>973200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1006900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1106300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1230400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>963300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>900700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1026500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>823400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>567300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>528700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>459400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>510700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>486900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>479400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>528700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>580200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>556200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>510100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>531900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>521700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>460300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>412500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>438400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>472000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>397200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E45" s="3">
         <v>40600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>37300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>41600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>33400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>32500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>41700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>53200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>28600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>21600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>21100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2502100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2505100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2415100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2267000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2262100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2436400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2376400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2472400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2073500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1922800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2122500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1737100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1538400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1512100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1236600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1060900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1093100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1092100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1097100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1103500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>995300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1046900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1112600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>863500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>888600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>894900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>899300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>756400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3994,192 +4098,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>880400</v>
+      </c>
+      <c r="E48" s="3">
         <v>845200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>823900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>816700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>796500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>745000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>733000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>700800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>685700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>647400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>630800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>586800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>494400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>483400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>478600</v>
       </c>
       <c r="R48" s="3">
         <v>478600</v>
       </c>
       <c r="S48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="T48" s="3">
         <v>467300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>460400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>439200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>422300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>354700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>346300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>340700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>313600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>328600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>325100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>316000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>309900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>297900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>518900</v>
+      </c>
+      <c r="E49" s="3">
         <v>476300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>481900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>487100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>488600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>440400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>445800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>445200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>431400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>393700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>424100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>415400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>331800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>311500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>300000</v>
       </c>
       <c r="R49" s="3">
         <v>300000</v>
       </c>
       <c r="S49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T49" s="3">
         <v>285200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>286600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>273800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>271300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>273000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>261700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>263000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>254500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>255000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>255700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>253500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>250200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>227600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,100 +4478,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E52" s="3">
         <v>177500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>123000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>126000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>124900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>43400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>19600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>18300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,100 +4668,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4017800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4004100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3843900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3696800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3672100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3738500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3610800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3674000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3245300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3014200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3228300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2786100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2404900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2350600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2058600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1883000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1889500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1880600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1850700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1821400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1647500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1677200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1736600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,141 +4835,145 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>203100</v>
+      </c>
+      <c r="E57" s="3">
         <v>253100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>264400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>278000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>206900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>323400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>386800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>426000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>319100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>292900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>359500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>299400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>211500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>231100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>199300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>162000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>142500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>180800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>189600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>170700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>136900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>175900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>197400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>176500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>140100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>171800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>160300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>156000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>124700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>45700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>52400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>104600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>34300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>2800</v>
       </c>
       <c r="Q58" s="3">
         <v>2800</v>
@@ -4852,414 +4985,429 @@
         <v>2800</v>
       </c>
       <c r="T58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>25100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>18900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>31300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>34200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>30500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>27200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>28800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>25100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>23800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>22400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E59" s="3">
         <v>347200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>289200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>249400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>402000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>433700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>384700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>372600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>397200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>361800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>337500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>264400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>252100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>259700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>233100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>164400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>208700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>204500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>164800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>131000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>145800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>151100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>138800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>106200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>136000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>138400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>126200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>98000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>124700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E60" s="3">
         <v>601800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>556000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>530400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>611800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>802900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>824000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>903200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>776000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>665700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>731300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>611000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>463700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>493600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>435200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>329300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>354000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>385400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>379600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>320600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>310200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>358300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>370400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>313100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>303200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>339000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>311600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>277800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>271800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E61" s="3">
         <v>273300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>274800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>275000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>275200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>275400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>276300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>379000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>277600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>310100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>571900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>426300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>311600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>311300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>161100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>160600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>160900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>162900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>187500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>266400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>202100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>186500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>276300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>261300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>144700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>145900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>204800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>252900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>109100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E62" s="3">
         <v>173400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>171300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>179000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>181400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>184000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>185400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>173600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>175100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>161000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>165500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>162200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>146400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>131900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>123000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>120900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>116800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>103200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>100300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>96000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>46600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>40600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>52000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>49300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>49600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>50800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,100 +5688,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1018000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1084700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1040600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1021000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1108100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1301500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1330700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1496100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1266700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1163500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1491800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1219900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>944600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>953000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>734200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>622300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>645800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>665200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>683300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>698500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>574100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>601100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>704100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>629900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>505200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>551100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>580300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>593100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>442900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5936,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,100 +6198,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2582300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2517300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2408300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2293000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2217400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2102800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1950900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1851800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1678100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1552600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1440800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1276700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1182700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1127400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1057800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>999000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>995000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>969600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>917700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>875500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>839900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>841400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>800200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>768200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>736200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>715500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>684800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>670100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>649100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,100 +6578,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2999800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2919400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2803400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2675800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2564000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2437100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2280100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2177900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1978600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1850800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1736500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1566200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1460300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1397600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1324400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1260700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1243700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1215500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1167400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1122900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1073400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1076100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1032500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>959500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>935800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>901700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>884500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>849200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44828</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44737</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44555</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44464</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44373</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44282</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E81" s="3">
         <v>127300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>263700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>120600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>127100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>160400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>377700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>182900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>133400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>117100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>267800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>100200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>61200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>75000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>103700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>39100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>50600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>87800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>34700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>40300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>43000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>30500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>33000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>53700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,100 +7000,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E83" s="3">
         <v>32600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>63200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>22700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>16300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>16600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>25600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,100 +7568,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E89" s="3">
         <v>390700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>321100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>298500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>442600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>90400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-245000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>230700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>397500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-115700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-196700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>151400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>37900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>147200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-46200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>151200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>127100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>70900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-55800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>56600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>96200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>39200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>82100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>36100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,100 +7700,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-60400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-79000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-18600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-23900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-42500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,100 +7983,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-102200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-131300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-103800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-59700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-82900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-514000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-296500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-53800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-66200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-48200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-36100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-58200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-64400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,74 +8115,75 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-18600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-31100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-15400</v>
       </c>
       <c r="H96" s="3">
         <v>-15400</v>
       </c>
       <c r="I96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="J96" s="3">
         <v>-28000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-9300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-18600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-7600</v>
       </c>
       <c r="P96" s="3">
         <v>-7600</v>
       </c>
       <c r="Q96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="R96" s="3">
         <v>-15400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-7700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-12300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-11000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7958,25 +8191,28 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,280 +8493,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-59400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-58600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-125000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>86300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-271500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>237900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>101900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>142200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-47000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-39700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-30300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>61100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>111600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>74500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>141700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E102" s="3">
         <v>257900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>143300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-135600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>109800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>311100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-152400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-216700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>135000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>111300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-391700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-391600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>89700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>145600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-135800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>103400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>43700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>28900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,426 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44828</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44737</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44555</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44464</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44282</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44191</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1639000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1524400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1827600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3866400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1822500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1913700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2322900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5390200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2489300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2016800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2093800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4525500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1825000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1393700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1486200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2274100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1032100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>998000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1163000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2254900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1015100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>988200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1212700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>993900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>966100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>846100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>859600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1312900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1228200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1463200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3108000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1464100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1556200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1872700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4408400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2011000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1645200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1766200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3817700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1538500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1206700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1245200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1901900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>864800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>840800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>975800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1914000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>860900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>850500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1054000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>863000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>836900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>911900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>725400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>737300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>326100</v>
+      </c>
+      <c r="E10" s="3">
         <v>296200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>364400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>758400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>358400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>357500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>450200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>981800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>478400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>371600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>327600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>707800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>286600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>187000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>241000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>372200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>167300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>157200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>187200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>341000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>154200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>137700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>158700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>165600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>130900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>129200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>144700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>269000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>120700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>122300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,8 +1122,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1204,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1316,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1394,8 +1414,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1547,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1505100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1400400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1660300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3511200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1660800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1745100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2085800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4845600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2230300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1821800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1925700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4151100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1687500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1305500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1379600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2123100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>973400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>946300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1092600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2132300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>966700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>942700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1155700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>949600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>924600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>812300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>824300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E18" s="3">
         <v>124000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>167300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>355200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>161700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>168600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>237100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>544600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>259000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>195000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>168100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>374400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>137500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>88200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>106600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>151000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>58700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>51700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>70400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>122600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>48400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>45500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>57000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>60600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>44300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>41500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>52300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>87700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>33800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,94 +1779,95 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E20" s="3">
         <v>14900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>200</v>
       </c>
       <c r="AA20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>400</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>100</v>
@@ -1841,153 +1875,159 @@
       <c r="AG20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E21" s="3">
         <v>175000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>209300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>431600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>198500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>208000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>263700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>590600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>283900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>223400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>192400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>422500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>161900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>110700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>126800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>185500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>73100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>71000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>88100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>157100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>66400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>60400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>73100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>75700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>58900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>55500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>66300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>113800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>46400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>48200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="E22" s="3">
         <v>3200</v>
       </c>
       <c r="F22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G22" s="3">
         <v>6400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3300</v>
       </c>
       <c r="L22" s="3">
         <v>3300</v>
       </c>
       <c r="M22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1900</v>
       </c>
       <c r="T22" s="3">
         <v>1900</v>
@@ -1996,233 +2036,242 @@
         <v>1900</v>
       </c>
       <c r="V22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W22" s="3">
         <v>4900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E23" s="3">
         <v>135700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>173500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>362100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>164500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>173000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>230700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>531100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>254100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>193100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>163400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>369900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>136000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>88100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>105700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>147200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>53900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>51600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>69000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>120100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>47600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>40900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>55300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>58600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>43200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>50900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>84800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>32400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>34100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E24" s="3">
         <v>31800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>85700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>130100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>46100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>90300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>26800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2365,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E26" s="3">
         <v>103900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>134200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>276400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>125600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>131900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>172100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>401000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>193100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>147000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>125700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>279600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>104300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>64800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>78900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>110300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>40600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>52600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>91100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>36000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>42100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>45100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>33600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>43500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>34700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>56200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E27" s="3">
         <v>98200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>127300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>263700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>120600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>127100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>160400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>377700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>182900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>133400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>267800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>61200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>75000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>103700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>39100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>36800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>50600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>87800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>34700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>21800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>40300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>43000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>32100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>40800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>53700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2648,8 +2709,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2666,11 +2727,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2678,11 +2739,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2696,8 +2757,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,94 +2953,97 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>-200</v>
       </c>
       <c r="AA32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>-100</v>
@@ -2981,103 +3051,109 @@
       <c r="AG32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E33" s="3">
         <v>98200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>127300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>263700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>120600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>127100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>160400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>377700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>182900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>133400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>267800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>61200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>75000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>103700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>39100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>36800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>50600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>87800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>34700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>40300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>43000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>32100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>30500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>53700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3247,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E35" s="3">
         <v>98200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>127300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>263700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>120600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>127100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>160400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>377700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>182900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>133400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>267800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>61200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>75000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>103700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>39100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>36800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>50600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>87800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>34700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>40300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>43000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>32100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>30500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>53700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44828</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44737</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44555</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44464</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44282</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44191</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,578 +3522,597 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>979700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1118300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>957100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>702100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>423300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>559400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>449100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>138100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>73800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>286700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>138600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>436500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>346200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>32100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>168300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>64500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>20500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>25300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>22000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>31000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>34100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E42" s="3">
         <v>34700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>38500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>37500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>36000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33100</v>
-      </c>
-      <c r="J42" s="3">
-        <v>35500</v>
       </c>
       <c r="K42" s="3">
         <v>35500</v>
       </c>
       <c r="L42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="M42" s="3">
         <v>36500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>33800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>31400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>24300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>20500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>19200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>17800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>18500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>17000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>16200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>15800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>14500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>722200</v>
+      </c>
+      <c r="E43" s="3">
         <v>582400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>725700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>819300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>814800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>657500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>915000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1066000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1102100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>748200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>801900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>984800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>811500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>480500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>587200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>527300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>469200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>382000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>483000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>489600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>456600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>364500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>469200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>497000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>432800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>335000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>422500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>398500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>368800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>293700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>745300</v>
+      </c>
+      <c r="E44" s="3">
         <v>727800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>744700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>821200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>960300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>973200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1006900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1106300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1230400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>963300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>900700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1026500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>823400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>567300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>528700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>459400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>510700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>486900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>479400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>528700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>580200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>556200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>510100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>531900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>521700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>460300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>412500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>438400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>472000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>397200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E45" s="3">
         <v>38800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>47900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>41600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>33400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>41700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>53200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>28600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>20700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>22900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>21600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>21100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2514400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2502100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2505100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2415100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2267000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2262100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2436400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2376400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2472400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2073500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1922800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2122500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1737100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1538400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1512100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1236600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1060900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1093100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1092100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1097100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1103500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>995300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1046900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>863500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>888600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>894900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>899300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>756400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4101,198 +4206,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>923400</v>
+      </c>
+      <c r="E48" s="3">
         <v>880400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>845200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>823900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>816700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>796500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>745000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>733000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>700800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>685700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>647400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>630800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>586800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>494400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>483400</v>
-      </c>
-      <c r="R48" s="3">
-        <v>478600</v>
       </c>
       <c r="S48" s="3">
         <v>478600</v>
       </c>
       <c r="T48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="U48" s="3">
         <v>467300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>460400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>439200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>422300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>354700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>346300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>340700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>313600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>328600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>325100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>316000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>309900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>297900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>511100</v>
+      </c>
+      <c r="E49" s="3">
         <v>518900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>476300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>481900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>487100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>488600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>440400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>445800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>445200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>431400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>393700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>424100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>415400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>331800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>311500</v>
-      </c>
-      <c r="R49" s="3">
-        <v>300000</v>
       </c>
       <c r="S49" s="3">
         <v>300000</v>
       </c>
       <c r="T49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="U49" s="3">
         <v>285200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>286600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>273800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>271300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>273000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>261700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>263000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>254500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>255000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>255700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>253500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>250200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>227600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,103 +4598,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E52" s="3">
         <v>116500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>177500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>123000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>126000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>124900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>43600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>41500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>40500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>19600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>18300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,103 +4794,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4078600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4017800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4004100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3843900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3696800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3672100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3738500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3610800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3674000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3245300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3014200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3228300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2786100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2404900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2350600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2058600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1883000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1889500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1880600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1850700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1821400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1647500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1677200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,147 +4966,151 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E57" s="3">
         <v>203100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>253100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>264400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>278000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>206900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>323400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>386800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>426000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>319100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>292900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>359500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>299400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>211500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>231100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>199300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>162000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>142500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>180800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>189600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>170700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>136900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>175900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>197400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>176500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>140100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>171800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>160300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>156000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>124700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E58" s="3">
         <v>42900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>52400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>104600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>59700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>34300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2800</v>
       </c>
       <c r="R58" s="3">
         <v>2800</v>
@@ -4988,426 +5122,441 @@
         <v>2800</v>
       </c>
       <c r="U58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>25100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>18900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>27500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>31300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>34200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>30500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>28800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>25100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>22400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E59" s="3">
         <v>322000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>347200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>289200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>249400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>402000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>433700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>384700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>372600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>397200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>361800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>337500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>264400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>252100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>259700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>233100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>164400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>208700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>204500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>164800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>131000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>145800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>151100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>138800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>106200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>136000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>138400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>126200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>98000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>124700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E60" s="3">
         <v>568000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>601800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>556000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>530400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>611800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>802900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>824000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>903200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>776000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>665700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>731300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>611000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>463700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>493600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>435200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>329300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>354000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>385400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>379600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>320600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>310200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>358300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>370400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>313100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>303200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>339000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>311600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>277800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>271800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E61" s="3">
         <v>233500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>273300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>274800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>275000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>275200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>275400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>276300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>379000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>277600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>310100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>571900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>426300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>311600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>311300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>161100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>160600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>160900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>162900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>187500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>266400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>202100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>186500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>276300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>261300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>144700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>145900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>204800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>252900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>109100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E62" s="3">
         <v>166100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>173400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>171300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>179000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>181400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>184000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>185400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>173600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>175100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>161000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>165500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>162200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>146400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>131900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>123000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>120900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>116800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>103200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>100300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>96000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>46600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>40600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>40100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>42700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>52000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>49300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>49600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>50800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,103 +5846,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>990900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1018000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1084700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1040600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1021000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1108100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1301500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1330700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1496100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1266700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1163500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1491800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1219900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>944600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>953000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>734200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>622300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>645800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>665200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>683300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>698500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>574100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>601100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>704100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>629900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>505200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>551100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>580300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>593100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>442900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,103 +6372,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2664100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2582300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2517300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2408300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2293000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2217400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2102800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1950900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1851800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1678100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1552600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1440800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1276700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1182700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1127400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1057800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>999000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>995000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>969600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>917700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>875500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>839900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>841400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>800200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>768200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>736200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>715500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>684800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>670100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>649100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,103 +6764,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3087800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2999800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2919400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2803400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2675800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2564000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2437100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2280100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2177900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1978600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1850800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1736500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1566200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1460300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1397600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1324400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1260700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1243700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1215500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1167400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1122900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1073400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1076100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>959500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>935800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>901700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>884500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>849200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6960,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44828</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44737</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44555</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44464</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44282</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44191</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E81" s="3">
         <v>98200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>127300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>263700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>120600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>127100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>160400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>377700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>182900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>133400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>267800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>61200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>75000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>103700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>39100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>36800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>50600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>87800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>34700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>40300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>43000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>32100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>30500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>53700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,103 +7199,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E83" s="3">
         <v>36100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>32600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>22700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>16300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>25600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7785,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E89" s="3">
         <v>248100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>390700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>321100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>298500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>442600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>90400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-245000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>230700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>397500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-115700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-196700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>151400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>37900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>147200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-46200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>151200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>127100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>70900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-55800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>56600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>96200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>39200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>82100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>36100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7921,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-60400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-79000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-34700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-46700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-23900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-42500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8213,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-52600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-102200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-85300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-131300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-103800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-59700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-82900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-514000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-296500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-34700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-66200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-48200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-36100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-58200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-47700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,77 +8349,78 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-18500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-18600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-31100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-15400</v>
       </c>
       <c r="I96" s="3">
         <v>-15400</v>
       </c>
       <c r="J96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-28000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-9300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-18600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-7600</v>
       </c>
       <c r="Q96" s="3">
         <v>-7600</v>
       </c>
       <c r="R96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="S96" s="3">
         <v>-15400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-7700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-12300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8194,25 +8428,28 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,289 +8739,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-36600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-58600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-125000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>86300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-271500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>237900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>101900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>142200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-47000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-39700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>61100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>111600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>74500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>141700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-141700</v>
+      </c>
+      <c r="E102" s="3">
         <v>161400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>257900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>143300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-135600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>109800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>311100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-152400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-216700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>135000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>111300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-391700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-391600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>89700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>145600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-135800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>103400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>28900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,439 +656,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44828</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44737</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44464</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44282</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1639000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1524400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1827600</v>
       </c>
-      <c r="G8" s="3">
-        <v>3866400</v>
-      </c>
       <c r="H8" s="3">
+        <v>2043900</v>
+      </c>
+      <c r="I8" s="3">
         <v>1822500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1913700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2322900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5390200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2489300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2016800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2093800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4525500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1825000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1393700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1486200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2274100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1032100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>998000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1163000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2254900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1015100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>988200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>993900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>966100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>846100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>859600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1539200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1312900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1228200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1463200</v>
       </c>
-      <c r="G9" s="3">
-        <v>3108000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1643900</v>
+      </c>
+      <c r="I9" s="3">
         <v>1464100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1556200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1872700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4408400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2011000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1645200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1766200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3817700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1538500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1206700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1245200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1901900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>864800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>840800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>975800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1914000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>860900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>850500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>863000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>836900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>911900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>725400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>737300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>362800</v>
+      </c>
+      <c r="E10" s="3">
         <v>326100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>296200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>364400</v>
       </c>
-      <c r="G10" s="3">
-        <v>758400</v>
-      </c>
       <c r="H10" s="3">
+        <v>400000</v>
+      </c>
+      <c r="I10" s="3">
         <v>358400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>357500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>450200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>981800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>478400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>371600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>327600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>707800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>286600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>187000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>241000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>372200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>167300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>157200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>187200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>341000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>154200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>137700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>158700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>165600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>130900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>129200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>144700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>269000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>120700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>122300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,8 +1136,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,8 +1336,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1417,8 +1437,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1574,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1742900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1505100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1660300</v>
       </c>
-      <c r="G17" s="3">
-        <v>3511200</v>
-      </c>
       <c r="H17" s="3">
+        <v>1850400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1660800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1745100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2085800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4845600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2230300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1821800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1925700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4151100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1687500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1305500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1379600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2123100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>973400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>946300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1092600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2132300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>966700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>942700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>949600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>924600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>812300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>824300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E18" s="3">
         <v>133900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>124000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>167300</v>
       </c>
-      <c r="G18" s="3">
-        <v>355200</v>
-      </c>
       <c r="H18" s="3">
+        <v>193500</v>
+      </c>
+      <c r="I18" s="3">
         <v>161700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>168600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>237100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>544600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>259000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>195000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>168100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>374400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>137500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>88200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>106600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>151000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>58700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>51700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>70400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>122600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>48400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>45500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>57000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>60600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>44300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>41500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>52300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>87700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>33800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>35300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,97 +1813,98 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E20" s="3">
         <v>15900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9400</v>
       </c>
-      <c r="G20" s="3">
-        <v>13300</v>
-      </c>
       <c r="H20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I20" s="3">
         <v>5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>200</v>
       </c>
       <c r="AB20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>400</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
@@ -1878,159 +1912,165 @@
       <c r="AH20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E21" s="3">
         <v>185600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>175000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>209300</v>
       </c>
-      <c r="G21" s="3">
-        <v>431600</v>
-      </c>
       <c r="H21" s="3">
+        <v>233200</v>
+      </c>
+      <c r="I21" s="3">
         <v>198500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>208000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>263700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>590600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>283900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>223400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>192400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>422500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>161900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>110700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>126800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>185500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>73100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>71000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>88100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>157100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>66400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>60400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>73100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>75700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>58900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>55500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>66300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>113800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>46400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>48200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E22" s="3">
         <v>3100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3200</v>
       </c>
       <c r="F22" s="3">
         <v>3200</v>
       </c>
       <c r="G22" s="3">
-        <v>6400</v>
+        <v>3200</v>
       </c>
       <c r="H22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I22" s="3">
         <v>3100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3300</v>
       </c>
       <c r="M22" s="3">
         <v>3300</v>
       </c>
       <c r="N22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O22" s="3">
         <v>3400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1900</v>
       </c>
       <c r="U22" s="3">
         <v>1900</v>
@@ -2039,239 +2079,248 @@
         <v>1900</v>
       </c>
       <c r="W22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X22" s="3">
         <v>4900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E23" s="3">
         <v>146600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>135700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>173500</v>
       </c>
-      <c r="G23" s="3">
-        <v>362100</v>
-      </c>
       <c r="H23" s="3">
+        <v>197500</v>
+      </c>
+      <c r="I23" s="3">
         <v>164500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>173000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>230700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>531100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>254100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>193100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>163400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>369900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>136000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>88100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>105700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>147200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>53900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>69000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>120100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>47600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>40900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>55300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>58600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>43200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>50900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>84800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>32400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>34100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E24" s="3">
         <v>25500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39300</v>
       </c>
-      <c r="G24" s="3">
-        <v>85700</v>
-      </c>
       <c r="H24" s="3">
+        <v>46700</v>
+      </c>
+      <c r="I24" s="3">
         <v>39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>58600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>130100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>61000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>90300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>17300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2417,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E26" s="3">
         <v>121100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>103900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>134200</v>
       </c>
-      <c r="G26" s="3">
-        <v>276400</v>
-      </c>
       <c r="H26" s="3">
+        <v>150800</v>
+      </c>
+      <c r="I26" s="3">
         <v>125600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>131900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>172100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>401000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>193100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>147000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>125700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>279600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>104300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>64800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>78900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>110300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>40600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>52600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>91100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>36000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>42100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>45100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>33600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>43500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>34700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>56200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E27" s="3">
         <v>120800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>98200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>127300</v>
       </c>
-      <c r="G27" s="3">
-        <v>263700</v>
-      </c>
       <c r="H27" s="3">
+        <v>137700</v>
+      </c>
+      <c r="I27" s="3">
         <v>120600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>127100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>160400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>377700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>182900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>133400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>117100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>267800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>61200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>75000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>103700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>39100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>50600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>87800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>21800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>40300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>43000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>32100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>40800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>33000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>53700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2712,8 +2773,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2730,11 +2791,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>8000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2742,11 +2803,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,97 +3023,100 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-13300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1600</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-200</v>
       </c>
       <c r="AB32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
@@ -3054,106 +3124,112 @@
       <c r="AH32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E33" s="3">
         <v>120800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>98200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>127300</v>
       </c>
-      <c r="G33" s="3">
-        <v>263700</v>
-      </c>
       <c r="H33" s="3">
+        <v>137700</v>
+      </c>
+      <c r="I33" s="3">
         <v>120600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>127100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>160400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>377700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>182900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>133400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>117100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>267800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>61200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>75000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>103700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>39100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>50600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>87800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>34700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>29800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>43000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>32100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>30500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>33000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>53700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3326,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E35" s="3">
         <v>120800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>98200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>127300</v>
       </c>
-      <c r="G35" s="3">
-        <v>263700</v>
-      </c>
       <c r="H35" s="3">
+        <v>137700</v>
+      </c>
+      <c r="I35" s="3">
         <v>120600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>127100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>160400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>377700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>182900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>133400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>117100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>267800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>61200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>75000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>103700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>39100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>50600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>87800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>34700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>29800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>43000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>32100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>30500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>33000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>53700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44828</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44737</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44464</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44282</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,596 +3609,615 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1041300</v>
+      </c>
+      <c r="E41" s="3">
         <v>979700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1118300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>957100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>702100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>423300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>559400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>449100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>138100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>73800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>286700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>138600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>436500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>346200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>32100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>168300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>64500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>20500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>17100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>25300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>31000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>34100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E42" s="3">
         <v>37000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>37100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>38500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>36000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33100</v>
-      </c>
-      <c r="K42" s="3">
-        <v>35500</v>
       </c>
       <c r="L42" s="3">
         <v>35500</v>
       </c>
       <c r="M42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="N42" s="3">
         <v>36500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>33700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>31400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>24300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>19200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>17800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>18500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>17000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>16800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>16200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>15800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>11300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>759600</v>
+      </c>
+      <c r="E43" s="3">
         <v>722200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>582400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>725700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>819300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>814800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>657500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>915000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1066000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1102100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>748200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>801900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>984800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>811500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>480500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>587200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>527300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>469200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>382000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>483000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>489600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>456600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>364500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>469200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>497000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>432800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>335000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>422500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>398500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>368800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>293700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>684800</v>
+      </c>
+      <c r="E44" s="3">
         <v>745300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>727800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>744700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>821200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>960300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>973200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1006900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1106300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1230400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>963300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>900700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1026500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>823400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>567300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>528700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>459400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>510700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>486900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>479400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>528700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>580200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>556200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>510100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>531900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>521700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>460300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>412500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>438400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>472000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>397200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E45" s="3">
         <v>30200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>48200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>41600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>33400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>32500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>41700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>53200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>22900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>21600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2554000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2514400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2502100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2505100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2415100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2267000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2262100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2436400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2376400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2472400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2073500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1922800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2122500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1737100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1538400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1512100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1236600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1060900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1093100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1092100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1097100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1103500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>995300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>863500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>888600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>894900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>899300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>756400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4209,204 +4314,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>944400</v>
+      </c>
+      <c r="E48" s="3">
         <v>923400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>880400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>845200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>823900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>816700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>796500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>745000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>733000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>700800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>685700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>647400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>630800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>586800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>494400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>483400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>478600</v>
       </c>
       <c r="T48" s="3">
         <v>478600</v>
       </c>
       <c r="U48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="V48" s="3">
         <v>467300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>460400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>439200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>422300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>354700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>346300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>340700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>313600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>328600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>325100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>316000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>309900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>297900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>505100</v>
+      </c>
+      <c r="E49" s="3">
         <v>511100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>518900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>476300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>481900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>487100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>488600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>440400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>445800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>445200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>431400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>393700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>424100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>415400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>331800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>311500</v>
-      </c>
-      <c r="S49" s="3">
-        <v>300000</v>
       </c>
       <c r="T49" s="3">
         <v>300000</v>
       </c>
       <c r="U49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="V49" s="3">
         <v>285200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>286600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>273800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>271300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>273000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>261700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>263000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>254500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>255000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>255700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>253500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>250200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>227600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,106 +4718,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E52" s="3">
         <v>129700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>116500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>177500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>123000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>126000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>124900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>55600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>40300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>41500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>40500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>22300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>19600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>18300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,106 +4920,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4138500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4078600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4017800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4004100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3843900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3696800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3672100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3738500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3610800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3674000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3245300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3014200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3228300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2786100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2404900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2350600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2058600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1883000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1889500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1880600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1850700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1821400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1647500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,153 +5097,157 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>263300</v>
+      </c>
+      <c r="E57" s="3">
         <v>254900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>203100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>253100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>264400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>278000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>206900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>323400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>386800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>426000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>319100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>292900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>359500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>299400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>211500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>231100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>199300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>162000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>142500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>180800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>189600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>170700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>136900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>175900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>197400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>176500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>140100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>171800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>160300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>156000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>124700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E58" s="3">
         <v>44100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>52400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>104600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>34300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>2800</v>
       </c>
       <c r="S58" s="3">
         <v>2800</v>
@@ -5125,242 +5259,251 @@
         <v>2800</v>
       </c>
       <c r="V58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>25100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>18900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>27500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>31300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>34200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>30500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>27200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>28800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>25100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>22400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>281300</v>
+      </c>
+      <c r="E59" s="3">
         <v>226100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>322000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>347200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>289200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>249400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>402000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>433700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>384700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>372600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>397200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>361800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>337500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>264400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>252100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>259700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>233100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>164400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>208700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>204500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>164800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>131000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>145800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>151100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>138800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>106200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>136000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>138400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>126200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>98000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>124700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E60" s="3">
         <v>525000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>568000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>601800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>556000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>530400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>611800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>802900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>824000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>903200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>776000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>665700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>731300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>611000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>463700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>493600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>435200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>329300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>354000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>385400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>379600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>320600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>310200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>358300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>370400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>313100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>303200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>339000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>311600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>277800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>271800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5368,195 +5511,201 @@
         <v>233000</v>
       </c>
       <c r="E61" s="3">
+        <v>233000</v>
+      </c>
+      <c r="F61" s="3">
         <v>233500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>273300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>274800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>275000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>275200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>275400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>276300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>379000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>277600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>310100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>571900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>426300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>311600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>311300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>161100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>160600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>160900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>162900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>187500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>266400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>202100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>186500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>276300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>261300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>144700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>145900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>204800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>252900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>109100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E62" s="3">
         <v>185100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>166100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>173400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>171300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>179000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>181400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>184000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>185400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>173600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>175100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>161000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>165500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>162200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>146400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>131900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>123000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>120900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>116800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>103200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>100300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>96000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>46600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>40100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>42700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>52000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>49300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>49600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,106 +6004,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1041700</v>
+      </c>
+      <c r="E66" s="3">
         <v>990900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1018000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1084700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1040600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1021000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1108100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1301500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1330700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1496100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1266700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1163500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1491800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1219900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>944600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>953000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>734200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>622300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>645800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>665200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>683300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>698500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>574100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>601100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>704100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>629900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>505200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>551100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>580300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>593100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>442900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,106 +6546,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2670100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2664100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2582300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2517300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2408300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2293000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2217400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2102800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1950900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1851800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1678100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1552600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1440800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1276700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1182700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1127400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1057800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>999000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>995000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>969600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>917700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>875500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>839900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>841400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>800200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>768200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>736200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>715500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>684800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>670100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>649100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,106 +6950,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3096800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3087800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2999800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2919400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2803400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2675800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2564000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2437100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2280100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2177900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1978600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1850800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1736500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1566200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1460300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1397600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1324400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1260700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1243700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1215500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1167400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1122900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1073400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>959500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>935800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>901700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>884500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>849200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7152,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44828</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44737</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44464</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44282</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E81" s="3">
         <v>120800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>98200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>127300</v>
       </c>
-      <c r="G81" s="3">
-        <v>263700</v>
-      </c>
       <c r="H81" s="3">
+        <v>137700</v>
+      </c>
+      <c r="I81" s="3">
         <v>120600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>127100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>160400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>377700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>182900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>133400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>117100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>267800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>61200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>75000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>103700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>39100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>50600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>87800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>34700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>29800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>43000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>32100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>30500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>33000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>53700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,106 +7398,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E83" s="3">
         <v>35900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32600</v>
       </c>
-      <c r="G83" s="3">
-        <v>63200</v>
-      </c>
       <c r="H83" s="3">
+        <v>32400</v>
+      </c>
+      <c r="I83" s="3">
         <v>30800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>52800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>22700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>25600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8002,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>248100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>390700</v>
       </c>
-      <c r="G89" s="3">
-        <v>321100</v>
-      </c>
       <c r="H89" s="3">
+        <v>358100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-37100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>298500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>442600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>90400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-245000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>230700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>397500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-115700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-196700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>151400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>37900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>147200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-46200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>151200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>127100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>70900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-55800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>56600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>96200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>48100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>39200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>82100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>15200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>36100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,106 +8142,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-60400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-79000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-42500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8443,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-102200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-85300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-41900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-131300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-103800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-82900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-514000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-296500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-53800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-66200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-48200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-58200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-47700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,80 +8583,81 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-20400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-18500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-18600</v>
       </c>
-      <c r="G96" s="3">
-        <v>-31100</v>
-      </c>
       <c r="H96" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="I96" s="3">
         <v>-15600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-15400</v>
       </c>
       <c r="J96" s="3">
         <v>-15400</v>
       </c>
       <c r="K96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="L96" s="3">
         <v>-28000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-12400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-18600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-7600</v>
       </c>
       <c r="R96" s="3">
         <v>-7600</v>
       </c>
       <c r="S96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="T96" s="3">
         <v>-15400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-7700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-12300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-12300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8431,25 +8665,28 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,298 +8985,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-127500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-69000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29200</v>
       </c>
-      <c r="G100" s="3">
-        <v>-97000</v>
-      </c>
       <c r="H100" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-59400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-58600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-26600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-125000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>86300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-271500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>237900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>101900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>142200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-47000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-39700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-30300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>61100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>111600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>74500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>141700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
-        <v>4600</v>
-      </c>
       <c r="H101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-141700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>161400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>257900</v>
       </c>
-      <c r="G102" s="3">
-        <v>143300</v>
-      </c>
       <c r="H102" s="3">
+        <v>278800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-135600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>109800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>311100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-152400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-216700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>135000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>111300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-391700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-391600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>89700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>145600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-135800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>103400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>28900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,452 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44828</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44737</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44464</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44373</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44282</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44191</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1649400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1902000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1639000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1524400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1827600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2043900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1822500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1913700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2322900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5390200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2489300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2016800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2093800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4525500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1825000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1393700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1486200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2274100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1032100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>998000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1163000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2254900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1015100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>988200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>993900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>966100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>846100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>859600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1351000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1539200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1312900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1228200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1463200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1643900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1464100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1556200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1872700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4408400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2011000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1645200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1766200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3817700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1538500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1206700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1245200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1901900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>864800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>840800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>975800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1914000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>860900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>850500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>863000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>836900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>911900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>725400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>737300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>362800</v>
+        <v>298400</v>
       </c>
       <c r="E10" s="3">
+        <v>362700</v>
+      </c>
+      <c r="F10" s="3">
         <v>326100</v>
       </c>
-      <c r="F10" s="3">
-        <v>296200</v>
-      </c>
       <c r="G10" s="3">
+        <v>296100</v>
+      </c>
+      <c r="H10" s="3">
         <v>364400</v>
       </c>
-      <c r="H10" s="3">
-        <v>400000</v>
-      </c>
       <c r="I10" s="3">
-        <v>358400</v>
+        <v>400100</v>
       </c>
       <c r="J10" s="3">
+        <v>358300</v>
+      </c>
+      <c r="K10" s="3">
         <v>357500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>450200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>981800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>478400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>371600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>327600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>707800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>286600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>187000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>241000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>372200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>167300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>157200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>187200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>341000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>154200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>137700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>158700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>165600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>130900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>129200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>144700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>269000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>120700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>122300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1137,8 +1150,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1238,8 +1252,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,31 +1356,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1440,31 +1460,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>37400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>36500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>36100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>32600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>32400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1529500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1742900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1505100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1660300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1850400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1660800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1745100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2085800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4845600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2230300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1821800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1925700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4151100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1687500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1305500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1379600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2123100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>973400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>946300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1092600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2132300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>966700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>942700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>949600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>924600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>812300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>824300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>159100</v>
+        <v>119900</v>
       </c>
       <c r="E18" s="3">
-        <v>133900</v>
+        <v>159000</v>
       </c>
       <c r="F18" s="3">
+        <v>133800</v>
+      </c>
+      <c r="G18" s="3">
         <v>124000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>167300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>193500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>161700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>168600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>237100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>544600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>259000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>195000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>168100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>374400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>137500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>88200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>106600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>151000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>58700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>51700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>70400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>122600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>48400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>45500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>57000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>60600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>44300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>41500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>52300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>87700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>33800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>35300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,100 +1847,101 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12500</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>15900</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
-        <v>14900</v>
+        <v>600</v>
       </c>
       <c r="G20" s="3">
-        <v>9400</v>
+        <v>1400</v>
       </c>
       <c r="H20" s="3">
-        <v>7300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>5900</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>600</v>
+      </c>
+      <c r="K20" s="3">
         <v>8200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>200</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
       </c>
       <c r="AC20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>400</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
@@ -1915,165 +1949,171 @@
       <c r="AI20" s="3">
         <v>100</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>208100</v>
+        <v>157200</v>
       </c>
       <c r="E21" s="3">
-        <v>185600</v>
+        <v>194900</v>
       </c>
       <c r="F21" s="3">
-        <v>175000</v>
+        <v>169100</v>
       </c>
       <c r="G21" s="3">
-        <v>209300</v>
+        <v>158800</v>
       </c>
       <c r="H21" s="3">
-        <v>233200</v>
+        <v>199900</v>
       </c>
       <c r="I21" s="3">
-        <v>198500</v>
+        <v>225500</v>
       </c>
       <c r="J21" s="3">
+        <v>191900</v>
+      </c>
+      <c r="K21" s="3">
         <v>208000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>263700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>590600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>283900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>223400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>192400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>422500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>161900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>110700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>126800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>185500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>73100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>71000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>88100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>157100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>66400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>60400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>73100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>75700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>58900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>55500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>66300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>113800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>46400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>48200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3200</v>
       </c>
       <c r="G22" s="3">
         <v>3200</v>
       </c>
       <c r="H22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I22" s="3">
         <v>3300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>3300</v>
       </c>
       <c r="N22" s="3">
         <v>3300</v>
       </c>
       <c r="O22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P22" s="3">
         <v>3400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3800</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1900</v>
       </c>
       <c r="V22" s="3">
         <v>1900</v>
@@ -2082,245 +2122,254 @@
         <v>1900</v>
       </c>
       <c r="X22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>4900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>134100</v>
+      </c>
+      <c r="E23" s="3">
         <v>168400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>146600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>135700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>173500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>197500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>164500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>173000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>230700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>531100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>254100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>193100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>163400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>369900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>136000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>88100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>105700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>147200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>53900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>51600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>69000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>120100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>47600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>40900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>55300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>58600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>43200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>40300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>50900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>84800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>32400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>34100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E24" s="3">
         <v>42200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>31800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>46700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>130100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>61000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>90300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>31800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>17300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>16300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E26" s="3">
         <v>126200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>121100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>103900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>134200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>150800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>125600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>172100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>401000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>193100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>147000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>125700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>279600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>104300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>64800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>78900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>110300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>40600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>38700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>52600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>91100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>42100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>45100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>43500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>34700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>56200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>22200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>125900</v>
+        <v>96000</v>
       </c>
       <c r="E27" s="3">
-        <v>120800</v>
+        <v>121100</v>
       </c>
       <c r="F27" s="3">
+        <v>115900</v>
+      </c>
+      <c r="G27" s="3">
         <v>98200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>127300</v>
       </c>
-      <c r="H27" s="3">
-        <v>137700</v>
-      </c>
       <c r="I27" s="3">
-        <v>120600</v>
+        <v>143200</v>
       </c>
       <c r="J27" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K27" s="3">
         <v>127100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>160400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>377700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>182900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>133400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>117100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>267800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>61200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>75000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>103700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>39100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>50600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>87800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>34700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>21800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>40300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>43000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>32100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>40800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>33000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>53700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2776,8 +2837,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2794,11 +2855,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2806,11 +2867,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2824,8 +2885,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,100 +3093,103 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12500</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-15900</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
-        <v>-14900</v>
+        <v>-600</v>
       </c>
       <c r="G32" s="3">
-        <v>-9400</v>
+        <v>-1400</v>
       </c>
       <c r="H32" s="3">
-        <v>-7300</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-5900</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-200</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
@@ -3127,109 +3197,115 @@
       <c r="AI32" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E33" s="3">
         <v>125900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>120800</v>
       </c>
-      <c r="F33" s="3">
-        <v>98200</v>
-      </c>
       <c r="G33" s="3">
-        <v>127300</v>
+        <v>103400</v>
       </c>
       <c r="H33" s="3">
-        <v>137700</v>
+        <v>134000</v>
       </c>
       <c r="I33" s="3">
-        <v>120600</v>
+        <v>150800</v>
       </c>
       <c r="J33" s="3">
+        <v>126100</v>
+      </c>
+      <c r="K33" s="3">
         <v>127100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>160400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>377700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>182900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>133400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>117100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>267800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>61200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>75000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>103700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>50600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>87800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>34700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>29800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>40300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>43000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>30500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>33000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>53700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E35" s="3">
         <v>125900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>120800</v>
       </c>
-      <c r="F35" s="3">
-        <v>98200</v>
-      </c>
       <c r="G35" s="3">
-        <v>127300</v>
+        <v>103400</v>
       </c>
       <c r="H35" s="3">
-        <v>137700</v>
+        <v>134000</v>
       </c>
       <c r="I35" s="3">
-        <v>120600</v>
+        <v>150800</v>
       </c>
       <c r="J35" s="3">
+        <v>126100</v>
+      </c>
+      <c r="K35" s="3">
         <v>127100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>160400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>377700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>182900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>133400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>117100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>267800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>61200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>75000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>103700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>50600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>87800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>34700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>29800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>40300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>43000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>30500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>33000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>53700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44828</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44737</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44464</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44373</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44282</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44191</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,637 +3696,656 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1190800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1041300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>979700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1118300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>957100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>702100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>423300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>559400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>449100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>138100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>73800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>286700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>138600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>436500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>346200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>32100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>168300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>64500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>25300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>31000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>34100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E42" s="3">
         <v>36700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>37000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>34700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>37100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>36000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33100</v>
-      </c>
-      <c r="L42" s="3">
-        <v>35500</v>
       </c>
       <c r="M42" s="3">
         <v>35500</v>
       </c>
       <c r="N42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="O42" s="3">
         <v>36500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>31400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>24300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>17800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>18500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>17000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>16800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>14800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>15800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>11300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>699800</v>
+      </c>
+      <c r="E43" s="3">
         <v>759600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>722200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>582400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>725700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>819300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>814800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>657500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>915000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1066000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1102100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>748200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>801900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>984800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>811500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>480500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>587200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>527300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>469200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>382000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>483000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>489600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>456600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>364500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>469200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>497000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>432800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>335000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>422500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>398500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>368800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>293700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>645400</v>
+      </c>
+      <c r="E44" s="3">
         <v>684800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>745300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>727800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>744700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>821200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>960300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>973200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1006900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1106300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1230400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>963300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>900700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1026500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>823400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>567300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>528700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>459400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>510700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>486900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>479400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>528700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>580200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>556200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>510100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>531900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>521700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>460300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>412500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>438400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>472000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>397200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>31500</v>
+        <v>37700</v>
       </c>
       <c r="E45" s="3">
-        <v>30200</v>
+        <v>30700</v>
       </c>
       <c r="F45" s="3">
+        <v>29400</v>
+      </c>
+      <c r="G45" s="3">
+        <v>34900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>36800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>33200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>30300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>32200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>30600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>30700</v>
+      </c>
+      <c r="O45" s="3">
         <v>38800</v>
       </c>
-      <c r="G45" s="3">
-        <v>40600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>34000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>31000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>35900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>32200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>30600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>30700</v>
-      </c>
-      <c r="N45" s="3">
-        <v>38800</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>30100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>37300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>48200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>41600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>33400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>32500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>41700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>53200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>28600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>22900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>21100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2613500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2554000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2514400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2502100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2505100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2415100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2267000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2262100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2436400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2376400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2472400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2073500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1922800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2122500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1737100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1538400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1512100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1236600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1060900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1093100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1092100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1097100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1103500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>995300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>863500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>888600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>894900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>899300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>756400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>116600</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>64300</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4317,210 +4422,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>967100</v>
+      </c>
+      <c r="E48" s="3">
         <v>944400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>923400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>880400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>845200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>823900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>816700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>796500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>745000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>733000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>700800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>685700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>647400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>630800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>586800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>494400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>483400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>478600</v>
       </c>
       <c r="U48" s="3">
         <v>478600</v>
       </c>
       <c r="V48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="W48" s="3">
         <v>467300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>460400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>439200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>422300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>354700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>346300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>340700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>313600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>328600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>325100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>316000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>309900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>297900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E49" s="3">
         <v>505100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>511100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>518900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>476300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>481900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>487100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>488600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>440400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>445800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>445200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>431400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>393700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>424100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>415400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>331800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>311500</v>
-      </c>
-      <c r="T49" s="3">
-        <v>300000</v>
       </c>
       <c r="U49" s="3">
         <v>300000</v>
       </c>
       <c r="V49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="W49" s="3">
         <v>285200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>286600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>273800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>271300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>273000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>261700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>263000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>254500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>255000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>255700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>253500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>250200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>227600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>134900</v>
+        <v>131500</v>
       </c>
       <c r="E52" s="3">
-        <v>129700</v>
+        <v>131600</v>
       </c>
       <c r="F52" s="3">
-        <v>116500</v>
+        <v>126100</v>
       </c>
       <c r="G52" s="3">
-        <v>177500</v>
+        <v>112300</v>
       </c>
       <c r="H52" s="3">
-        <v>123000</v>
+        <v>57400</v>
       </c>
       <c r="I52" s="3">
-        <v>126000</v>
+        <v>54500</v>
       </c>
       <c r="J52" s="3">
+        <v>121800</v>
+      </c>
+      <c r="K52" s="3">
         <v>124900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>116800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>55500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>41500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>40500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>19600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>17700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>18300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4217900</v>
+      </c>
+      <c r="E54" s="3">
         <v>4138500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4078600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4017800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4004100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3843900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3696800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3672100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3738500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3610800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3674000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3245300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3014200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3228300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2786100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2404900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2350600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2058600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1883000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1889500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1880600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1850700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1821400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,159 +5228,163 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>239900</v>
+      </c>
+      <c r="E57" s="3">
         <v>263300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>254900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>203100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>253100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>264400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>278000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>206900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>323400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>386800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>426000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>319100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>292900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>359500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>299400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>211500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>231100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>199300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>162000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>142500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>180800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>189600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>170700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>136900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>175900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>197400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>176500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>140100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>171800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>160300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>156000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>124700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>43800</v>
+        <v>72500</v>
       </c>
       <c r="E58" s="3">
-        <v>44100</v>
+        <v>71800</v>
       </c>
       <c r="F58" s="3">
-        <v>42900</v>
+        <v>70600</v>
       </c>
       <c r="G58" s="3">
-        <v>1500</v>
+        <v>65900</v>
       </c>
       <c r="H58" s="3">
-        <v>2400</v>
+        <v>25900</v>
       </c>
       <c r="I58" s="3">
-        <v>3000</v>
+        <v>28300</v>
       </c>
       <c r="J58" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K58" s="3">
         <v>2900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>52400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>104600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>59700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>34300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2800</v>
       </c>
       <c r="T58" s="3">
         <v>2800</v>
@@ -5262,450 +5396,465 @@
         <v>2800</v>
       </c>
       <c r="W58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>25100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>27500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>34200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>30500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>27200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>28800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>25100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>23800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>22400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>281300</v>
+        <v>8700</v>
       </c>
       <c r="E59" s="3">
-        <v>226100</v>
+        <v>8800</v>
       </c>
       <c r="F59" s="3">
-        <v>322000</v>
+        <v>10100</v>
       </c>
       <c r="G59" s="3">
-        <v>347200</v>
+        <v>9500</v>
       </c>
       <c r="H59" s="3">
-        <v>289200</v>
+        <v>10300</v>
       </c>
       <c r="I59" s="3">
-        <v>249400</v>
+        <v>12900</v>
       </c>
       <c r="J59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K59" s="3">
         <v>402000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>433700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>384700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>372600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>397200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>361800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>337500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>264400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>252100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>259700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>233100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>164400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>208700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>204500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>164800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>131000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>145800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>151100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>138800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>106200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>136000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>138400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>126200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>98000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>124700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E60" s="3">
         <v>588400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>525000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>568000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>601800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>556000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>530400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>611800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>802900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>824000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>903200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>776000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>665700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>731300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>611000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>463700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>493600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>435200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>329300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>354000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>385400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>379600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>320600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>310200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>358300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>370400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>313100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>303200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>339000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>311600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>277800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>271800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>233000</v>
+        <v>333800</v>
       </c>
       <c r="E61" s="3">
-        <v>233000</v>
+        <v>335900</v>
       </c>
       <c r="F61" s="3">
-        <v>233500</v>
+        <v>339300</v>
       </c>
       <c r="G61" s="3">
-        <v>273300</v>
+        <v>318400</v>
       </c>
       <c r="H61" s="3">
-        <v>274800</v>
+        <v>359900</v>
       </c>
       <c r="I61" s="3">
-        <v>275000</v>
+        <v>359000</v>
       </c>
       <c r="J61" s="3">
+        <v>367200</v>
+      </c>
+      <c r="K61" s="3">
         <v>275200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>275400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>276300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>379000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>277600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>310100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>571900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>426300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>311600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>311300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>161100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>160600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>160900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>162900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>187500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>266400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>202100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>186500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>276300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>261300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>144700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>145900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>204800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>252900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>109100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>180700</v>
+        <v>34000</v>
       </c>
       <c r="E62" s="3">
-        <v>185100</v>
+        <v>33000</v>
       </c>
       <c r="F62" s="3">
-        <v>166100</v>
+        <v>34100</v>
       </c>
       <c r="G62" s="3">
-        <v>173400</v>
+        <v>20400</v>
       </c>
       <c r="H62" s="3">
-        <v>171300</v>
+        <v>36000</v>
       </c>
       <c r="I62" s="3">
-        <v>179000</v>
+        <v>36100</v>
       </c>
       <c r="J62" s="3">
+        <v>35600</v>
+      </c>
+      <c r="K62" s="3">
         <v>181400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>184000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>185400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>173600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>175100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>161000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>165500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>162200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>146400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>123000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>120900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>116800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>103200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>100300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>96000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>46600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>40600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>42300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>40100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>42700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>52000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>49300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1041700</v>
+        <v>1018500</v>
       </c>
       <c r="E66" s="3">
-        <v>990900</v>
+        <v>1002100</v>
       </c>
       <c r="F66" s="3">
-        <v>1018000</v>
+        <v>943200</v>
       </c>
       <c r="G66" s="3">
-        <v>1084700</v>
+        <v>967600</v>
       </c>
       <c r="H66" s="3">
-        <v>1040600</v>
+        <v>1048500</v>
       </c>
       <c r="I66" s="3">
-        <v>1021000</v>
+        <v>1002200</v>
       </c>
       <c r="J66" s="3">
+        <v>984300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1108100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1301500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1330700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1496100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1266700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1163500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1491800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1219900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>944600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>953000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>734200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>622300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>645800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>665200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>683300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>698500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>574100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>601100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>704100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>629900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>505200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>551100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>580300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>593100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>442900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2728300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2670100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2664100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2582300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2517300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2408300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2293000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2217400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2102800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1950900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1851800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1678100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1552600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1440800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1276700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1182700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1127400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1057800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>999000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>995000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>969600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>917700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>875500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>839900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>841400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>800200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>768200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>736200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>715500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>684800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>670100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>649100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3174400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3096800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3087800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2999800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2919400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2803400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2675800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2564000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2437100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2280100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2177900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1978600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1850800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1736500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1566200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1460300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1397600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1324400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1260700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1243700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1215500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1167400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1122900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>959500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>935800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>901700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>884500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>849200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44828</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44737</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44464</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44373</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44282</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44191</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E81" s="3">
         <v>125900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>120800</v>
       </c>
-      <c r="F81" s="3">
-        <v>98200</v>
-      </c>
       <c r="G81" s="3">
-        <v>127300</v>
+        <v>103400</v>
       </c>
       <c r="H81" s="3">
-        <v>137700</v>
+        <v>134000</v>
       </c>
       <c r="I81" s="3">
-        <v>120600</v>
+        <v>150800</v>
       </c>
       <c r="J81" s="3">
+        <v>126100</v>
+      </c>
+      <c r="K81" s="3">
         <v>127100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>160400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>377700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>182900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>133400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>117100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>267800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>61200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>75000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>103700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>50600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>87800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>34700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>29800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>40300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>43000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>30500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>33000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>53700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>36500</v>
+        <v>27600</v>
       </c>
       <c r="E83" s="3">
-        <v>35900</v>
+        <v>27000</v>
       </c>
       <c r="F83" s="3">
-        <v>36100</v>
+        <v>25800</v>
       </c>
       <c r="G83" s="3">
-        <v>32600</v>
+        <v>25200</v>
       </c>
       <c r="H83" s="3">
-        <v>32400</v>
+        <v>24800</v>
       </c>
       <c r="I83" s="3">
-        <v>30800</v>
+        <v>22200</v>
       </c>
       <c r="J83" s="3">
+        <v>21800</v>
+      </c>
+      <c r="K83" s="3">
         <v>31200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>52800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>19600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>34500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>25600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E89" s="3">
         <v>255900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>248100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>390700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>358100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>298500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>442600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>90400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-245000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>230700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>397500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-115700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-196700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>151400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>37900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>147200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-46200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>151200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>127100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>70900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-55800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>56600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>96200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>48100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>39200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>82100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>15200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>36100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-57400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-46700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-23900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-102200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-131300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-103800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-118800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-82900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-514000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-296500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-53800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-66200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-48200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-36100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-58200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-47700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,83 +8817,84 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-20200</v>
+        <v>20100</v>
       </c>
       <c r="E96" s="3">
-        <v>-20400</v>
+        <v>20200</v>
       </c>
       <c r="F96" s="3">
-        <v>-18500</v>
+        <v>20400</v>
       </c>
       <c r="G96" s="3">
-        <v>-18600</v>
+        <v>18500</v>
       </c>
       <c r="H96" s="3">
-        <v>-15500</v>
+        <v>18600</v>
       </c>
       <c r="I96" s="3">
-        <v>-15600</v>
+        <v>15500</v>
       </c>
       <c r="J96" s="3">
-        <v>-15400</v>
+        <v>15600</v>
       </c>
       <c r="K96" s="3">
         <v>-15400</v>
       </c>
       <c r="L96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="M96" s="3">
         <v>-28000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-12500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-12400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-7600</v>
       </c>
       <c r="S96" s="3">
         <v>-7600</v>
       </c>
       <c r="T96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="U96" s="3">
         <v>-15400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-7700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-12300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8668,25 +8902,28 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9231,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-127500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-69000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-36600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-59400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-58600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-125000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>86300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-271500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>237900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>101900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>142200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-47000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-39700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>61100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>111600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>74500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>141700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-3800</v>
+        <v>-1400</v>
       </c>
       <c r="E101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="R101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T101" s="3">
+        <v>300</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I101" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="V101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W101" s="3">
+        <v>300</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="V101" s="3">
-        <v>300</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>200</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>900</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-400</v>
-      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E102" s="3">
         <v>61600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-141700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>161400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>257900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>278800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-135600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>109800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>311100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-152400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-216700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>135000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>111300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-391700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-391600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>89700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>145600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-135800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>103400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>43700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>28900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -656,465 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44828</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44737</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44464</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44282</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44191</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1462000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1649400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1902000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1639000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1524400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1827600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2043900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1822500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1913700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2322900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5390200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2489300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2016800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2093800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4525500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1825000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1393700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1486200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2274100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1032100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>998000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1163000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2254900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1015100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>988200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>993900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>966100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>846100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>859600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1222500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1351000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1539200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1312900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1228200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1463200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1643900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1464100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1556200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1872700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4408400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2011000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1645200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1766200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3817700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1538500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1206700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1245200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1901900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>864800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>840800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>975800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1914000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>860900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>850500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>863000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>836900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>911900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>725400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>737300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E10" s="3">
         <v>298400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>362700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>326100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>296100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>364400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>400100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>358300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>357500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>450200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>981800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>478400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>371600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>327600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>707800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>286600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>187000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>241000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>372200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>167300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>157200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>187200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>341000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>154200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>137700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>158700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>165600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>130900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>129200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>144700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>269000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>120700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,8 +1163,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1255,8 +1268,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,13 +1375,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>6200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1376,8 +1395,8 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>-300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1385,8 +1404,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1463,35 +1482,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E15" s="3">
         <v>37400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>35900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>32600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1567,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1376400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1529500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1742900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1505100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1400400</v>
-      </c>
       <c r="H17" s="3">
+        <v>1400600</v>
+      </c>
+      <c r="I17" s="3">
         <v>1660300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1850400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1660800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1745100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2085800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4845600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2230300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1821800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1925700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4151100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1687500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1305500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1379600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2123100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>973400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>946300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1092600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2132300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>966700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>942700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>949600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>924600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>812300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>824300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E18" s="3">
         <v>119900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>159000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>133800</v>
       </c>
-      <c r="G18" s="3">
-        <v>124000</v>
-      </c>
       <c r="H18" s="3">
+        <v>123700</v>
+      </c>
+      <c r="I18" s="3">
         <v>167300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>193500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>161700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>168600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>237100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>544600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>259000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>195000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>168100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>374400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>137500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>88200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>106600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>151000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>58700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>51700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>70400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>122600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>48400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>45500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>60600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>44300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>41500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>52300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>87700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>33800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>35300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,103 +1880,104 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>600</v>
       </c>
       <c r="F20" s="3">
         <v>600</v>
       </c>
       <c r="G20" s="3">
+        <v>600</v>
+      </c>
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
       </c>
       <c r="AD20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>400</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>100</v>
       </c>
       <c r="AI20" s="3">
         <v>100</v>
@@ -1952,171 +1985,177 @@
       <c r="AJ20" s="3">
         <v>100</v>
       </c>
+      <c r="AK20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E21" s="3">
         <v>157200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>194900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>169100</v>
       </c>
-      <c r="G21" s="3">
-        <v>158800</v>
-      </c>
       <c r="H21" s="3">
+        <v>158500</v>
+      </c>
+      <c r="I21" s="3">
         <v>199900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>225500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>191900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>208000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>263700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>590600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>283900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>223400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>192400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>422500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>161900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>110700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>126800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>185500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>73100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>71000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>88100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>157100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>66400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>60400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>73100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>75700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>58900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>55500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>66300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>113800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>46400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="3">
         <v>3000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3200</v>
       </c>
       <c r="H22" s="3">
         <v>3200</v>
       </c>
       <c r="I22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J22" s="3">
         <v>3300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6700</v>
-      </c>
-      <c r="N22" s="3">
-        <v>3300</v>
       </c>
       <c r="O22" s="3">
         <v>3300</v>
       </c>
       <c r="P22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3800</v>
-      </c>
-      <c r="V22" s="3">
-        <v>1900</v>
       </c>
       <c r="W22" s="3">
         <v>1900</v>
@@ -2125,251 +2164,260 @@
         <v>1900</v>
       </c>
       <c r="Y22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z22" s="3">
         <v>4900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E23" s="3">
         <v>134100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>168400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>146600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>135700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>173500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>197500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>164500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>173000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>230700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>531100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>254100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>193100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>163400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>369900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>136000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>88100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>105700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>147200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>53900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>51600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>69000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>120100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>47600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>40900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>55300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>58600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>43200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>40300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>50900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>84800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>32400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>34100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E24" s="3">
         <v>32500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>42200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>31800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>46700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>130100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>46100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>90300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>31800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>17300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>16300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>28600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E26" s="3">
         <v>101600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>126200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>121100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>103900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>134200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>150800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>125600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>131900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>172100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>401000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>193100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>147000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>125700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>279600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>104300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>64800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>78900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>110300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>40600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>38700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>52600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>91100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>23600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>42100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>45100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>33600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>43500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>34700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>56200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E27" s="3">
         <v>96000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>121100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>115900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>98200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>127300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>143200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>120500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>127100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>160400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>377700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>182900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>133400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>267800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>61200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>75000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>103700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>39100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>36800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>50600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>87800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>21800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>40300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>43000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>32100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>40800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>33000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>53700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2841,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2840,8 +2900,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2858,11 +2918,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2870,11 +2930,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2888,8 +2948,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,103 +3162,106 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-600</v>
       </c>
       <c r="F32" s="3">
         <v>-600</v>
       </c>
       <c r="G32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-100</v>
       </c>
       <c r="AI32" s="3">
         <v>-100</v>
@@ -3200,112 +3269,118 @@
       <c r="AJ32" s="3">
         <v>-100</v>
       </c>
+      <c r="AK32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E33" s="3">
         <v>99800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>125900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>120800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>103400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>134000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>150800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>126100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>127100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>160400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>377700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>182900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>133400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>267800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>61200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>75000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>103700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>36800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>50600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>87800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>40300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>32100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>30500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>33000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>53700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E35" s="3">
         <v>99800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>125900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>120800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>103400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>134000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>150800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>126100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>127100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>160400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>377700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>182900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>133400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>267800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>61200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>75000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>103700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>36800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>50600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>87800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>40300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>32100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>30500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>33000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>53700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44828</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44737</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44464</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44282</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44191</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,637 +3782,656 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1171800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1190800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1041300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>979700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1118300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>957100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>702100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>423300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>559400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>449100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>138100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>73800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>286700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>138600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>44300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>436500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>346200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>32100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>168300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>20500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>17100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>25300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>22000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>31000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>34100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E42" s="3">
         <v>38900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>36700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>37000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>34700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33100</v>
-      </c>
-      <c r="M42" s="3">
-        <v>35500</v>
       </c>
       <c r="N42" s="3">
         <v>35500</v>
       </c>
       <c r="O42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="P42" s="3">
         <v>36500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>31400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>24300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>17800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>16200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>15800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E43" s="3">
         <v>699800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>759600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>722200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>582400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>725700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>819300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>814800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>657500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>915000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1066000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1102100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>748200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>801900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>984800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>811500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>480500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>587200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>527300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>469200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>382000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>483000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>489600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>456600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>364500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>469200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>497000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>432800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>335000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>422500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>398500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>368800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>720800</v>
+      </c>
+      <c r="E44" s="3">
         <v>645400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>684800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>745300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>727800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>744700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>821200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>960300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>973200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1006900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1106300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1230400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>963300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>900700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1026500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>823400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>567300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>528700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>459400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>510700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>486900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>479400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>528700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>580200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>556200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>510100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>531900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>521700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>460300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>412500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>438400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>472000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>397200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E45" s="3">
         <v>37700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>47900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>37300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>48200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>41600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>33400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>32500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>25400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>41700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>53200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>28600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>20700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>22900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>21600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>21100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2503000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2613500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2554000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2514400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2502100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2505100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2415100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2267000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2262100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2436400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2376400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2472400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2073500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1922800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2122500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1737100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1538400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1512100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1236600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1060900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1093100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1092100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1097100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1103500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>995300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>863500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>888600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>894900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>899300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>756400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>56400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4338,18 +4442,18 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>116600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64300</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4425,216 +4529,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1005500</v>
+      </c>
+      <c r="E48" s="3">
         <v>967100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>944400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>923400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>880400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>845200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>823900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>816700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>796500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>745000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>733000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>685700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>647400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>630800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>586800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>494400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>483400</v>
-      </c>
-      <c r="U48" s="3">
-        <v>478600</v>
       </c>
       <c r="V48" s="3">
         <v>478600</v>
       </c>
       <c r="W48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="X48" s="3">
         <v>467300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>460400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>439200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>422300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>354700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>346300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>340700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>313600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>328600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>325100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>316000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>309900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>297900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>499600</v>
+      </c>
+      <c r="E49" s="3">
         <v>501600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>505100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>511100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>518900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>476300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>481900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>487100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>488600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>440400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>445800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>445200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>431400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>393700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>424100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>415400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>331800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>311500</v>
-      </c>
-      <c r="U49" s="3">
-        <v>300000</v>
       </c>
       <c r="V49" s="3">
         <v>300000</v>
       </c>
       <c r="W49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="X49" s="3">
         <v>285200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>286600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>273800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>271300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>273000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>261700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>263000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>254500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>255000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>255700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>253500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>250200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>227600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +4957,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E52" s="3">
         <v>131500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>131600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>126100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>112300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>121800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>124900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>116800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>55600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>50900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>46900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>40300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>43900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>41500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>40500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>20300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>19600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>17500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>18300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5171,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4150900</v>
+      </c>
+      <c r="E54" s="3">
         <v>4217900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4138500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4078600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4017800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4004100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3843900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3696800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3672100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3738500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3610800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3674000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3245300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3014200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3228300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2786100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2404900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2350600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2058600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1883000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1889500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1880600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1850700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1821400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,165 +5358,169 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E57" s="3">
         <v>239900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>263300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>254900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>203100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>253100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>264400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>278000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>206900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>323400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>386800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>426000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>319100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>292900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>359500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>299400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>211500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>231100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>199300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>162000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>142500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>180800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>189600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>170700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>136900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>175900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>197400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>176500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>140100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>171800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>160300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>156000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>124700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E58" s="3">
         <v>72500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>70600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>65900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>28300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>30900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>52400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>104600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>59700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>34300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>47200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
-      </c>
-      <c r="T58" s="3">
-        <v>2800</v>
       </c>
       <c r="U58" s="3">
         <v>2800</v>
@@ -5399,462 +5532,477 @@
         <v>2800</v>
       </c>
       <c r="X58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>25100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>27500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>31300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>34200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>30500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>27200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>28800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>25100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>23800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E59" s="3">
         <v>8700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>402000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>433700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>384700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>372600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>397200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>361800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>337500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>264400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>252100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>259700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>233100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>164400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>208700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>204500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>164800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>131000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>145800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>151100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>138800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>106200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>136000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>138400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>126200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>98000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>124700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>512400</v>
+      </c>
+      <c r="E60" s="3">
         <v>606000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>588400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>525000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>568000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>601800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>556000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>530400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>611800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>802900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>824000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>903200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>776000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>665700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>731300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>611000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>463700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>493600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>435200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>329300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>354000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>385400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>379600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>320600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>310200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>358300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>370400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>313100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>303200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>339000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>311600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>277800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324900</v>
+      </c>
+      <c r="E61" s="3">
         <v>333800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>335900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>339300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>318400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>359900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>359000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>367200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>275200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>275400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>276300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>379000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>277600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>310100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>571900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>426300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>311600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>311300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>161100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>160600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>160900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>162900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>187500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>266400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>202100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>186500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>276300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>261300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>144700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>145900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>204800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>252900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E62" s="3">
         <v>34000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>181400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>184000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>185400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>173600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>175100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>161000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>165500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>162200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>146400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>131900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>123000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>120900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>116800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>103200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>100300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>96000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>46600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>40600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>42300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>42700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>52000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>49600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6319,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1018500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1002100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>943200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>967600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1048500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1002200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>984300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1108100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1301500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1330700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1496100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1266700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1163500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1491800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1219900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>944600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>953000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>734200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>622300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>645800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>665200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>683300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>698500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>574100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>601100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>704100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>629900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>505200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>551100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>580300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>593100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>442900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +6893,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2775300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2728300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2670100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2664100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2582300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2517300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2408300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2293000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2217400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2102800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1950900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1851800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1678100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1552600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1440800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1276700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1182700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1127400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1057800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>999000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>995000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>969600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>917700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>875500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>839900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>841400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>800200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>768200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>736200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>715500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>684800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>670100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>649100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7321,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3224100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3174400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3096800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3087800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2999800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2919400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2803400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2675800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2564000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2437100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2280100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2177900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1978600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1850800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1736500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1566200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1460300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1397600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1324400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1260700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1243700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1215500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1167400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1122900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>959500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>935800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>901700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>884500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>849200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44828</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44737</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44464</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44282</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44191</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E81" s="3">
         <v>99800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>125900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>120800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>103400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>134000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>150800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>126100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>127100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>160400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>377700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>182900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>133400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>267800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>61200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>75000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>103700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>36800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>50600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>87800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>40300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>32100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>30500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>33000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>53700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7795,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E83" s="3">
         <v>27600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>52800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>19600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>18600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>34500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>14900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>25600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E89" s="3">
         <v>258600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>255900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>248100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>390700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>358100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>298500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>442600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>90400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-245000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>230700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>397500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-115700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-196700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>151400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>37900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>147200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-46200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>151200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>127100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>70900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-55800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>56600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>96200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>48100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>39200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>82100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-57400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-79000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-93300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-63000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-52600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-102200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-131300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-103800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-118800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-82900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-514000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-296500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-53800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-66200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-48200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-36100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-58200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-47700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8827,77 +9060,77 @@
         <v>20100</v>
       </c>
       <c r="E96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F96" s="3">
         <v>20200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>20400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>18500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>18600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>15500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>15600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-15400</v>
       </c>
       <c r="L96" s="3">
         <v>-15400</v>
       </c>
       <c r="M96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="N96" s="3">
         <v>-28000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-12500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-12400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-18600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-7600</v>
       </c>
       <c r="T96" s="3">
         <v>-7600</v>
       </c>
       <c r="U96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="V96" s="3">
         <v>-15400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-7700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-12300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8905,25 +9138,28 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,316 +9476,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-61400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-127500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-69000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-36600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-37700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-59400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-58600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-125000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>86300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-271500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>237900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>101900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>142200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-47000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-39700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-30300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>61100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>111600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>74500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>141700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>149500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>61600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-141700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>161400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>257900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>278800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-135600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>109800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>311100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-152400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-216700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>135000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>111300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-391700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-391600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>89700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>145600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-135800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>103400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>28900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -656,477 +656,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44828</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44737</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44464</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44282</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44191</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1595500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1462000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1649400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1902000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1639000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1524400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1827600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2043900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1822500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1913700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2322900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5390200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2489300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2016800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2093800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4525500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1825000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1393700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1486200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2274100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1032100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>998000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1163000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2254900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1015100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>988200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>993900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>966100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>846100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>859600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1327300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1222500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1351000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1539200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1312900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1228200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1463200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1643900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1464100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1556200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1872700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4408400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2011000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1645200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1766200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3817700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1538500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1206700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1245200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1901900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>864800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>840800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>975800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1914000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>860900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>850500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>863000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>836900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>911900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>725400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>737300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E10" s="3">
         <v>239500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>298400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>362700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>326100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>296100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>364400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>400100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>358300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>357500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>450200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>981800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>478400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>371600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>327600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>707800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>286600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>187000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>241000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>372200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>167300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>157200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>187200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>341000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>154200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>137700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>158700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>165600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>130900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>129200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>144700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>269000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>120700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>122300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1164,8 +1177,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1271,8 +1285,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1378,16 +1395,19 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1396,10 +1416,10 @@
         <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1407,8 +1427,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1485,38 +1505,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E15" s="3">
         <v>38400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>37400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>32600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>30800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1592,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,222 +1654,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1503300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1376400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1529500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1742900</v>
       </c>
-      <c r="G17" s="3">
-        <v>1505100</v>
-      </c>
       <c r="H17" s="3">
+        <v>1505400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1400600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1660300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1850400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1660800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1745100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2085800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4845600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2230300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1821800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1925700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4151100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1687500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1305500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1379600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2123100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>973400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>946300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1092600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>966700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>942700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>949600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>924600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>812300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>824300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E18" s="3">
         <v>85600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>119900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>159000</v>
       </c>
-      <c r="G18" s="3">
-        <v>133800</v>
-      </c>
       <c r="H18" s="3">
+        <v>133600</v>
+      </c>
+      <c r="I18" s="3">
         <v>123700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>167300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>193500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>161700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>168600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>237100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>544600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>259000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>195000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>168100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>374400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>137500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>88200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>106600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>151000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>58700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>70400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>122600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>48400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>45500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>57000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>60600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>44300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>41500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>52300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>87700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>35300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,106 +1914,107 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>600</v>
       </c>
       <c r="G20" s="3">
         <v>600</v>
       </c>
       <c r="H20" s="3">
+        <v>600</v>
+      </c>
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
       <c r="AE20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>400</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>100</v>
@@ -1988,177 +2022,183 @@
       <c r="AK20" s="3">
         <v>100</v>
       </c>
+      <c r="AL20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E21" s="3">
         <v>125400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>157200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>194900</v>
       </c>
-      <c r="G21" s="3">
-        <v>169100</v>
-      </c>
       <c r="H21" s="3">
+        <v>168900</v>
+      </c>
+      <c r="I21" s="3">
         <v>158500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>199900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>225500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>191900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>208000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>263700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>590600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>283900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>223400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>192400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>422500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>161900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>110700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>126800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>185500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>73100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>71000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>88100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>157100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>66400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>60400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>73100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>75700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>58900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>55500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>66300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>113800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>48200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>3500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3200</v>
       </c>
       <c r="I22" s="3">
         <v>3200</v>
       </c>
       <c r="J22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K22" s="3">
         <v>3300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>3300</v>
       </c>
       <c r="P22" s="3">
         <v>3300</v>
       </c>
       <c r="Q22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R22" s="3">
         <v>3400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3800</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1900</v>
       </c>
       <c r="X22" s="3">
         <v>1900</v>
@@ -2167,257 +2207,266 @@
         <v>1900</v>
       </c>
       <c r="Z22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>4900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E23" s="3">
         <v>91000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>134100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>168400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>146600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>135700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>173500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>197500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>164500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>173000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>230700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>531100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>254100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>193100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>163400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>369900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>136000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>88100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>105700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>147200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>53900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>51600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>69000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>120100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>47600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>55300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>58600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>43200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>40300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>50900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>84800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>34100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E24" s="3">
         <v>21200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>31800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>46700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>41200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>130100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>61000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>90300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>31800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>26800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>16300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>28600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>11900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,222 +2572,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E26" s="3">
         <v>69800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>101600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>126200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>121100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>103900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>134200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>150800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>125600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>172100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>401000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>193100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>147000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>125700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>279600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>104300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>64800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>78900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>110300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>40600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>38700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>52600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>91100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>36000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>42100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>45100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>33600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>43500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>34700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>56200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>22200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E27" s="3">
         <v>65400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>96000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>121100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>115900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>98200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>127300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>143200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>120500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>127100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>160400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>377700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>182900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>133400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>117100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>267800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>61200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>75000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>103700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>39100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>36800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>50600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>87800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>40300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>43000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>32100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>40800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>33000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>53700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2902,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2903,8 +2964,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2921,11 +2982,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2933,11 +2994,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2951,8 +3012,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,106 +3232,109 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-600</v>
       </c>
       <c r="G32" s="3">
         <v>-600</v>
       </c>
       <c r="H32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
       <c r="AE32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>-100</v>
@@ -3272,115 +3342,121 @@
       <c r="AK32" s="3">
         <v>-100</v>
       </c>
+      <c r="AL32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E33" s="3">
         <v>68000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>99800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>125900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>120800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>103400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>134000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>150800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>126100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>127100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>160400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>377700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>182900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>133400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>117100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>267800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>61200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>75000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>103700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>39100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>36800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>50600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>87800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>34700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>29800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>40300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>43000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>32100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>30500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>33000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>53700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,227 +3562,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E35" s="3">
         <v>68000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>99800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>125900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>120800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>103400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>134000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>150800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>126100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>127100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>160400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>377700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>182900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>133400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>117100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>267800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>61200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>75000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>103700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>39100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>36800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>50600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>87800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>34700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>29800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>40300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>43000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>32100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>30500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>33000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>53700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44828</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44737</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44464</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44282</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44191</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,658 +3869,677 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>903600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1171800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1190800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1041300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>979700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1118300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>957100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>702100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>423300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>559400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>449100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>138100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>73800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>286700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>138600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>436500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>346200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>32100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>168300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>64500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>17100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>25300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>34100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E42" s="3">
         <v>31100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>36700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>37000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>34700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33100</v>
-      </c>
-      <c r="N42" s="3">
-        <v>35500</v>
       </c>
       <c r="O42" s="3">
         <v>35500</v>
       </c>
       <c r="P42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="Q42" s="3">
         <v>36500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>31400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>24300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>20500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>19200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>17800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>18500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>17000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>16800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>16200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>15800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>11300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>723100</v>
+      </c>
+      <c r="E43" s="3">
         <v>529000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>699800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>759600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>722200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>582400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>725700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>819300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>814800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>657500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>915000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1066000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1102100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>748200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>801900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>984800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>811500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>480500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>587200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>527300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>469200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>382000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>483000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>489600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>456600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>364500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>469200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>497000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>432800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>335000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>422500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>398500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>368800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>293700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>754900</v>
+      </c>
+      <c r="E44" s="3">
         <v>720800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>645400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>684800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>745300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>727800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>744700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>821200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>960300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>973200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1006900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1106300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1230400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>963300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1026500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>823400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>567300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>528700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>459400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>510700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>486900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>479400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>528700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>580200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>556200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>510100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>531900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>521700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>460300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>412500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>438400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>472000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>397200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E45" s="3">
         <v>42500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>30100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>37300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>48200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>41600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>33400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>25400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>41700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>53200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>28600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>20700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>22900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>21600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>21100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2464400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2503000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2613500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2554000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2514400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2502100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2505100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2415100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2267000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2262100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2436400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2376400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2472400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2073500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1922800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2122500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1737100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1538400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1512100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1236600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1060900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1093100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1092100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1097100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1103500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>995300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>863500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>888600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>894900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>899300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>756400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E47" s="3">
         <v>56400</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -4445,18 +4550,18 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>116600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64300</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4532,222 +4637,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1039500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1005500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>967100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>944400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>923400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>880400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>845200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>823900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>816700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>796500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>745000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>733000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>685700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>647400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>630800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>586800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>494400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>483400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>478600</v>
       </c>
       <c r="W48" s="3">
         <v>478600</v>
       </c>
       <c r="X48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>467300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>460400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>439200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>422300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>354700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>346300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>340700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>313600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>328600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>325100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>316000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>309900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>297900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>495900</v>
+      </c>
+      <c r="E49" s="3">
         <v>499600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>501600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>505100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>511100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>518900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>476300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>481900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>487100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>488600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>440400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>445800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>445200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>431400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>393700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>424100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>415400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>331800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>311500</v>
-      </c>
-      <c r="V49" s="3">
-        <v>300000</v>
       </c>
       <c r="W49" s="3">
         <v>300000</v>
       </c>
       <c r="X49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>285200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>286600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>273800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>271300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>273000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>261700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>263000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>254500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>255000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>255700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>253500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>250200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>227600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,115 +5077,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E52" s="3">
         <v>81100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>131500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>131600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>126100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>54500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>121800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>124900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>54600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>50400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>50900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>46900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>40300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>43500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>41500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>40500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>19600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>17600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>17700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,115 +5297,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4150300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4150900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4217900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4138500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4078600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4017800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4004100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3843900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3696800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3672100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3738500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3610800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3674000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3245300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3014200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3228300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2786100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2404900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2350600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2058600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1883000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1889500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1880600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1850700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1821400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,171 +5489,175 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>277700</v>
+      </c>
+      <c r="E57" s="3">
         <v>224700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>239900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>263300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>254900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>203100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>253100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>264400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>278000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>206900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>323400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>386800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>426000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>319100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>292900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>359500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>299400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>211500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>231100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>199300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>162000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>142500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>180800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>189600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>170700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>136900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>175900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>197400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>176500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>140100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>171800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>160300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>156000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>124700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E58" s="3">
         <v>32000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>72500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>71800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>70600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>65900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>25900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>28300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>30900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>52400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>34300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>47200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>2800</v>
       </c>
       <c r="V58" s="3">
         <v>2800</v>
@@ -5535,474 +5669,489 @@
         <v>2800</v>
       </c>
       <c r="Y58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>25100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>18900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>31300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>34200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>30500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>27200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>28800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>25100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>23800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>22400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>402000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>433700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>384700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>372600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>397200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>361800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>337500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>264400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>252100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>259700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>233100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>164400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>208700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>204500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>164800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>131000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>145800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>151100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>138800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>106200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>136000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>138400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>126200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>98000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>124700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E60" s="3">
         <v>512400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>606000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>588400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>525000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>568000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>601800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>556000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>530400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>611800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>802900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>824000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>903200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>776000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>665700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>731300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>611000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>463700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>493600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>435200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>329300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>354000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>385400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>379600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>320600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>310200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>358300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>370400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>313100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>303200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>339000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>311600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>277800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>271800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>326200</v>
+      </c>
+      <c r="E61" s="3">
         <v>324900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>333800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>335900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>339300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>318400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>359900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>359000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>367200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>275200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>275400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>276300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>379000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>277600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>310100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>571900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>426300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>311600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>311300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>161100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>160600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>160900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>162900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>187500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>266400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>202100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>186500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>276300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>261300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>144700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>145900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>204800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>252900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>109100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E62" s="3">
         <v>15400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>181400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>184000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>185400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>173600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>175100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>161000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>165500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>162200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>146400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>131900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>123000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>120900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>116800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>103200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>100300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>96000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>40600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>42300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>40100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>42700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>52000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>49300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>49600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,115 +6477,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E66" s="3">
         <v>900900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1018500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1002100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>943200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>967600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1048500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1002200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>984300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1108100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1301500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1330700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1496100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1266700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1163500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1491800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1219900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>944600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>953000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>734200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>622300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>645800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>665200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>683300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>698500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>574100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>601100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>704100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>629900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>505200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>551100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>580300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>593100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>442900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,115 +7067,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2772800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2775300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2728300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2670100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2664100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2582300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2517300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2408300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2293000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2217400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2102800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1950900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1851800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1678100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1552600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1440800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1276700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1182700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1127400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1057800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>999000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>995000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>969600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>917700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>875500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>839900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>841400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>800200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>768200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>736200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>715500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>684800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>670100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>649100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,115 +7507,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3237700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3224100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3174400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3096800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3087800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2999800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2919400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2803400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2675800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2564000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2437100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2280100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2177900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1978600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1850800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1736500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1566200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1460300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1397600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1324400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1260700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1243700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1215500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1167400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1122900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>959500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>935800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>901700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>884500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>849200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,227 +7727,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44828</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44737</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44464</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44282</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44191</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E81" s="3">
         <v>68000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>99800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>125900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>120800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>103400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>134000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>150800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>126100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>127100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>160400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>377700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>182900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>133400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>117100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>267800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>61200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>75000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>103700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>39100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>36800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>50600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>87800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>34700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>29800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>40300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>43000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>32100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>30500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>33000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>53700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,115 +7994,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E83" s="3">
         <v>30100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>52800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>34500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>14900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>25600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>12700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,115 +8652,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-108800</v>
+      </c>
+      <c r="E89" s="3">
         <v>144900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>258600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>255900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>248100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>390700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>358100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>298500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>442600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>90400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-245000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>230700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>397500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-115700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-196700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>151400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>147200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-46200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>151200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>127100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>70900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-55800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>56600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>96200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>48100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>39200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>82100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>15200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>36100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,115 +8804,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-57400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-49100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-79000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,115 +9132,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-93300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-52600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-102200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-43500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-131300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-103800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-118800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-59700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-514000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-296500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-53800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-66200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-48200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-58200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-47700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,89 +9284,90 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>20100</v>
+        <v>21300</v>
       </c>
       <c r="E96" s="3">
         <v>20100</v>
       </c>
       <c r="F96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G96" s="3">
         <v>20200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>20400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>18500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>18600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>15500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>15600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-15400</v>
       </c>
       <c r="M96" s="3">
         <v>-15400</v>
       </c>
       <c r="N96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="O96" s="3">
         <v>-28000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-12500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-18600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-7600</v>
       </c>
       <c r="U96" s="3">
         <v>-7600</v>
       </c>
       <c r="V96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="W96" s="3">
         <v>-15400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-7700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -9141,25 +9375,28 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,325 +9722,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-90900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-61400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-49200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-127500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-69000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-58600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-26600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-125000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>86300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-271500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>237900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>101900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>142200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-47000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-39700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>61100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>111600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>74500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>141700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>149500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>61600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-141700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>161400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>257900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>278800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-135600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>109800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>311100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-152400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-216700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>135000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>111300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-391700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-391600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>89700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>145600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-135800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>103400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>43700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,490 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44828</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44737</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44464</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44282</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44191</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1835400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1595500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1462000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1649400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1902000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1639000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1524400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1827600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2043900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1822500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1913700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2322900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5390200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2489300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2016800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2093800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4525500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1825000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1393700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1486200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2274100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1032100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>998000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1163000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2254900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1015100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>988200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>993900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>966100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>846100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>859600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1522600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1327300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1222500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1351000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1539200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1312900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1228200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1463200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1643900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1464100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1556200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1872700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4408400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2011000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1645200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1766200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3817700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1538500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1206700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1245200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1901900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>864800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>840800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>975800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1914000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>860900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>850500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>863000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>836900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>911900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>725400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>737300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>312700</v>
+      </c>
+      <c r="E10" s="3">
         <v>268200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>239500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>298400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>362700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>326100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>296100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>364400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>400100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>358300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>357500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>450200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>981800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>478400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>371600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>327600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>707800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>286600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>187000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>241000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>372200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>167300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>157200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>187200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>341000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>154200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>137700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>158700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>165600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>130900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>129200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>144700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>269000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>120700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>122300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,8 +1191,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1288,8 +1302,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1398,31 +1415,34 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1430,8 +1450,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1508,41 +1528,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E15" s="3">
         <v>38800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>37400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>35900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>32600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30800</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1618,8 +1641,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,228 +1681,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1708500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1503300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1376400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1529500</v>
       </c>
-      <c r="G17" s="3">
-        <v>1742900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1740700</v>
+      </c>
+      <c r="I17" s="3">
         <v>1505400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1400600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1660300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1850400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1660800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1745100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2085800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4845600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2230300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1821800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1925700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4151100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1687500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1305500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1379600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2123100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>973400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>946300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1092600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>966700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>942700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>949600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>924600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>812300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>824300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E18" s="3">
         <v>92200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>85600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>119900</v>
       </c>
-      <c r="G18" s="3">
-        <v>159000</v>
-      </c>
       <c r="H18" s="3">
+        <v>161300</v>
+      </c>
+      <c r="I18" s="3">
         <v>133600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>123700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>167300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>193500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>161700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>168600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>237100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>544600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>259000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>195000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>168100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>374400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>137500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>88200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>106600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>151000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>51700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>70400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>122600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>48400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>45500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>57000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>60600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>44300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>41500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>52300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>87700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>33800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>35300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,109 +1948,110 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
       </c>
       <c r="H20" s="3">
         <v>600</v>
       </c>
       <c r="I20" s="3">
+        <v>600</v>
+      </c>
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>200</v>
       </c>
       <c r="AE20" s="3">
         <v>200</v>
       </c>
       <c r="AF20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>400</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>100</v>
       </c>
       <c r="AK20" s="3">
         <v>100</v>
@@ -2025,118 +2059,124 @@
       <c r="AL20" s="3">
         <v>100</v>
       </c>
+      <c r="AM20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>167700</v>
+      </c>
+      <c r="E21" s="3">
         <v>130900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>125400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>157200</v>
       </c>
-      <c r="G21" s="3">
-        <v>194900</v>
-      </c>
       <c r="H21" s="3">
+        <v>197100</v>
+      </c>
+      <c r="I21" s="3">
         <v>168900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>158500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>199900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>225500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>191900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>208000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>263700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>590600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>283900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>223400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>192400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>422500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>161900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>110700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>126800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>185500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>73100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>71000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>88100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>157100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>66400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>60400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>73100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>75700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>58900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>55500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>66300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>113800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>46400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>48200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2144,64 +2184,64 @@
         <v>2700</v>
       </c>
       <c r="E22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F22" s="3">
         <v>3500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3200</v>
       </c>
       <c r="J22" s="3">
         <v>3200</v>
       </c>
       <c r="K22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L22" s="3">
         <v>3300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>3300</v>
       </c>
       <c r="Q22" s="3">
         <v>3300</v>
       </c>
       <c r="R22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S22" s="3">
         <v>3400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3800</v>
-      </c>
-      <c r="X22" s="3">
-        <v>1900</v>
       </c>
       <c r="Y22" s="3">
         <v>1900</v>
@@ -2210,263 +2250,272 @@
         <v>1900</v>
       </c>
       <c r="AA22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB22" s="3">
         <v>4900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E23" s="3">
         <v>100700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>91000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>134100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>168400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>146600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>135700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>173500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>197500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>164500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>173000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>230700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>531100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>254100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>193100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>163400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>369900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>136000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>88100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>105700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>147200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>53900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>51600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>69000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>120100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>47600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>55300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>58600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>43200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>40300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>50900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>84800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>32400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>34100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E24" s="3">
         <v>21300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>32500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>42200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>41200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>58600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>130100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>61000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>90300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>23300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>26800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,228 +2624,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E26" s="3">
         <v>79400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>69800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>101600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>126200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>121100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>103900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>134200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>150800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>125600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>172100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>401000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>193100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>147000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>125700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>279600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>104300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>64800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>78900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>110300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>40600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>38700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>52600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>91100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>36000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>42100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>45100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>33600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>43500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>34700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>56200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>21600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>22200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E27" s="3">
         <v>75800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>96000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>121100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>115900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>98200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>127300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>143200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>120500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>127100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>160400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>377700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>182900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>133400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>117100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>267800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>61200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>75000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>103700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>36800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>50600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>87800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>34700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>40300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>43000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>32100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>40800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>33000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2963,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2967,8 +3028,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2985,11 +3046,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2997,11 +3058,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3015,8 +3076,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3189,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,109 +3302,112 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
       </c>
       <c r="H32" s="3">
         <v>-600</v>
       </c>
       <c r="I32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-200</v>
       </c>
       <c r="AE32" s="3">
         <v>-200</v>
       </c>
       <c r="AF32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-100</v>
       </c>
       <c r="AK32" s="3">
         <v>-100</v>
@@ -3345,118 +3415,124 @@
       <c r="AL32" s="3">
         <v>-100</v>
       </c>
+      <c r="AM32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E33" s="3">
         <v>78800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>68000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>99800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>125900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>120800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>103400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>134000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>150800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>126100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>127100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>160400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>377700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>182900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>133400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>117100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>267800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>61200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>75000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>103700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>36800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>50600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>87800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>34700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>40300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>43000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>32100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>30500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>33000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,233 +3641,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E35" s="3">
         <v>78800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>68000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>99800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>125900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>120800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>103400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>134000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>150800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>126100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>127100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>160400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>377700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>182900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>133400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>117100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>267800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>61200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>75000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>103700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>36800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>50600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>87800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>34700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>40300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>43000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>32100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>30500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>33000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44828</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44737</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44464</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44282</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44191</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3915,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,701 +3956,720 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>841900</v>
+      </c>
+      <c r="E41" s="3">
         <v>903600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1171800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1190800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1041300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>979700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1118300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>957100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>702100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>423300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>559400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>449100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>138100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>73800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>286700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>138600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>436500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>346200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>200500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>168300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>64500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>17100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>25300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>28300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>22000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>31000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>34100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E42" s="3">
         <v>30700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>31100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>38900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>34700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>33100</v>
-      </c>
-      <c r="O42" s="3">
-        <v>35500</v>
       </c>
       <c r="P42" s="3">
         <v>35500</v>
       </c>
       <c r="Q42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="R42" s="3">
         <v>36500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>33800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>31400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>24300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>20500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>18500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>17000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>16800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>16200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>15800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>11300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>715200</v>
+      </c>
+      <c r="E43" s="3">
         <v>723100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>529000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>699800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>759600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>722200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>582400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>725700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>819300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>814800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>657500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>915000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1066000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1102100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>748200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>801900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>984800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>811500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>480500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>587200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>527300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>469200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>382000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>483000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>489600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>456600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>364500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>469200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>497000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>432800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>335000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>422500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>398500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>368800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>293700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>722200</v>
+      </c>
+      <c r="E44" s="3">
         <v>754900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>720800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>645400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>684800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>745300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>727800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>744700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>821200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>960300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>973200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1006900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1106300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1230400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>963300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>900700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1026500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>823400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>567300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>528700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>459400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>510700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>486900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>479400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>528700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>580200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>556200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>510100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>531900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>521700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>460300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>412500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>438400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>472000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>397200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E45" s="3">
         <v>51100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>47900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>33100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>30100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>37300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>48200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>41600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>33400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>41700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>53200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>28600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>20700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>22900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>21600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>21100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2367500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2464400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2503000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2613500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2554000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2514400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2502100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2505100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2415100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2267000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2262100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2436400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2376400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2472400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2073500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1922800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2122500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1737100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1538400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1512100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1236600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1060900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1093100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1092100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1097100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1103500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>995300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>863500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>888600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>894900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>899300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>756400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E47" s="3">
         <v>55400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>56400</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+      <c r="H47" s="3">
+        <v>22000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>116600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>64300</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4640,228 +4745,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1076900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1039500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1005500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>967100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>944400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>923400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>880400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>845200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>823900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>816700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>796500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>745000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>733000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>685700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>647400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>630800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>586800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>494400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>483400</v>
-      </c>
-      <c r="W48" s="3">
-        <v>478600</v>
       </c>
       <c r="X48" s="3">
         <v>478600</v>
       </c>
       <c r="Y48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="Z48" s="3">
         <v>467300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>460400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>439200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>422300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>354700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>346300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>340700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>313600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>328600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>325100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>316000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>309900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>297900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E49" s="3">
         <v>495900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>499600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>501600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>505100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>511100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>518900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>476300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>481900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>487100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>488600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>440400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>445800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>445200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>431400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>393700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>424100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>415400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>331800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>311500</v>
-      </c>
-      <c r="W49" s="3">
-        <v>300000</v>
       </c>
       <c r="X49" s="3">
         <v>300000</v>
       </c>
       <c r="Y49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>285200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>286600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>273800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>271300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>273000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>261700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>263000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>254500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>255000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>255700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>253500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>250200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>227600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5084,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,118 +5197,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E52" s="3">
         <v>90300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>81100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>131500</v>
       </c>
-      <c r="G52" s="3">
-        <v>131600</v>
-      </c>
       <c r="H52" s="3">
+        <v>109600</v>
+      </c>
+      <c r="I52" s="3">
         <v>126100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>121800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>124900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>116800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>54600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>50400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>50900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>46900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>43400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>41500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>40500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>19600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>17600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>17500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>17700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>18300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,118 +5423,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4097400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4150300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4150900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4217900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4138500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4078600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4017800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4004100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3843900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3696800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3672100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3738500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3610800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3674000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3245300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3014200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3228300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2786100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2404900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2350600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2058600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1883000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1889500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1880600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1850700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1821400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5579,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,177 +5620,181 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>258800</v>
+      </c>
+      <c r="E57" s="3">
         <v>277700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>224700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>239900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>263300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>254900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>203100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>253100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>264400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>278000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>206900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>323400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>386800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>426000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>319100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>292900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>359500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>299400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>211500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>231100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>199300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>162000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>142500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>180800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>189600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>170700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>136900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>175900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>197400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>176500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>140100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>171800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>160300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>156000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>124700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E58" s="3">
         <v>32100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>72500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>71800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>70600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>65900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>25900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>28300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>30900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>45700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>52400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>104600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>59700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>34300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>47200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>100</v>
-      </c>
-      <c r="V58" s="3">
-        <v>2800</v>
       </c>
       <c r="W58" s="3">
         <v>2800</v>
@@ -5672,486 +5806,501 @@
         <v>2800</v>
       </c>
       <c r="Z58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>25100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>27500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>31300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>34200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>30500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>27200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>28800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>23800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>22400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>402000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>433700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>384700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>372600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>397200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>361800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>337500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>264400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>252100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>259700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>233100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>164400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>208700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>204500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>164800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>145800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>151100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>138800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>106200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>136000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>138400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>126200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>98000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>124700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>521100</v>
+      </c>
+      <c r="E60" s="3">
         <v>496500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>512400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>606000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>588400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>525000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>568000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>601800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>556000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>530400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>611800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>802900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>824000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>903200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>776000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>665700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>731300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>611000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>463700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>493600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>435200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>329300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>354000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>385400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>379600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>320600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>310200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>358300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>370400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>313100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>303200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>339000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>311600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>277800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>271800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E61" s="3">
         <v>326200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>324900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>333800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>335900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>339300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>318400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>359900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>359000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>367200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>275200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>275400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>276300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>379000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>277600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>310100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>571900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>426300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>311600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>311300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>161100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>160600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>160900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>162900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>187500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>266400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>202100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>186500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>276300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>261300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>144700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>145900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>204800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>252900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>109100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E62" s="3">
         <v>32600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>181400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>184000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>185400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>173600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>175100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>161000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>165500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>162200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>146400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>131900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>123000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>120900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>116800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>103200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>100300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>96000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>42300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>40100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>52000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>49300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>49600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>50800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6409,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6522,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,118 +6635,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>923700</v>
+      </c>
+      <c r="E66" s="3">
         <v>886000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1018500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1002100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>943200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>967600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1048500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1002200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>984300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1108100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1301500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1330700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1496100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1266700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1163500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1491800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1219900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>944600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>953000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>734200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>622300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>645800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>665200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>683300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>698500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>574100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>601100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>704100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>629900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>505200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>551100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>580300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>593100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>442900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6791,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6902,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7015,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6960,8 +7128,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,118 +7241,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2663400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2772800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2775300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2728300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2670100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2664100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2582300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2517300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2408300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2293000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2217400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2102800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1950900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1851800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1678100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1552600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1440800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1276700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1182700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1127400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1057800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>999000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>995000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>969600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>917700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>875500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>839900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>841400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>800200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>768200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>736200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>715500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>684800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>670100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>649100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7467,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7580,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,118 +7693,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3145400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3237700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3224100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3174400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3096800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3087800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2999800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2919400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2803400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2675800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2564000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2437100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2280100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2177900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1978600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1850800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1736500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1566200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1460300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1397600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1324400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1260700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1243700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1215500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1167400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1122900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>959500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>935800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>901700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>884500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>849200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,233 +7919,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44828</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44737</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44464</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44282</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44191</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E81" s="3">
         <v>78800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>68000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>99800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>125900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>120800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>103400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>134000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>150800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>126100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>127100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>160400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>377700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>182900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>133400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>117100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>267800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>61200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>75000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>103700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>36800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>50600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>87800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>34700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>40300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>43000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>32100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>30500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>33000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,118 +8193,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E83" s="3">
         <v>30000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>52800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>34500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>16600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>15900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>25600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>12500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>12700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8417,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8530,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8643,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8756,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,118 +8869,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>221900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-108800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>144900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>258600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>255900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>248100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>390700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>358100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>298500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>442600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>90400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-245000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>230700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>397500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-115700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-196700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>151400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>147200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-46200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>151200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>127100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>70900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-55800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>56600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>96200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>48100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>39200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>82100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>36100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,118 +9025,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-67300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-49400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-60400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-79000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-42500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9249,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,118 +9362,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-93300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-63000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-52600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-102200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-131300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-103800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-118800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-82900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-514000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-296500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-53800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-34700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-66200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-48200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-58200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-47700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,92 +9518,93 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E96" s="3">
         <v>21300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>20100</v>
       </c>
       <c r="F96" s="3">
         <v>20100</v>
       </c>
       <c r="G96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="H96" s="3">
         <v>20200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>20400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>18500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>18600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>15500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>15600</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-15400</v>
       </c>
       <c r="N96" s="3">
         <v>-15400</v>
       </c>
       <c r="O96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="P96" s="3">
         <v>-28000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-12400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-18600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-7600</v>
       </c>
       <c r="V96" s="3">
         <v>-7600</v>
       </c>
       <c r="W96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="X96" s="3">
         <v>-15400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9378,25 +9612,28 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9742,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9855,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,334 +9968,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-211400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-90900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-61400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-49200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-127500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-69000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-59400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-58600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-26600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-125000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>86300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-271500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>237900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>101900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>142200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-47000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-39700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>61100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>111600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>74500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>141700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-275000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>149500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>61600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-141700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>161400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>257900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>278800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-135600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>311100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-152400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-216700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>135000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>111300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-391700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-391600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>89700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>145600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>32600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-135800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>103400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>43700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44828</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44737</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44464</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44282</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44191</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1329800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1559600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1835400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1595500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1462000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1649400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1902000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1639000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1524400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1827600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2043900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1822500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1913700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2322900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5390200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2489300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2016800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2093800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4525500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1825000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1393700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1486200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2274100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1032100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>998000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1163000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2254900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1015100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>988200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>993900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>966100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>846100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>859600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1113300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1296900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1522600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1327300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1222500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1351000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1539200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1312900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1228200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1463200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1643900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1464100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1556200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1872700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4408400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2011000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1645200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1766200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3817700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1538500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1206700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1245200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1901900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>864800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>840800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>975800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1914000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>860900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>850500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>863000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>836900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>911900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>725400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>737300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>216500</v>
+      </c>
+      <c r="E10" s="3">
         <v>262700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>312700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>268200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>239500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>298400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>362700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>326100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>296100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>364400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>358300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>357500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>450200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>981800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>478400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>371600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>327600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>707800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>286600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>187000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>241000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>372200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>167300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>157200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>187200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>341000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>154200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>137700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>158700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>165600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>130900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>129200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>144700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>269000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>120700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>122300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1206,8 +1218,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1322,8 +1335,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1438,37 +1454,40 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>6200</v>
-      </c>
       <c r="H14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1476,8 +1495,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1554,47 +1573,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E15" s="3">
         <v>40600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>38800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>38400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30800</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1692,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1709,240 +1734,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1275800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1467700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1708500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1503300</v>
       </c>
-      <c r="G17" s="3">
-        <v>1376400</v>
-      </c>
       <c r="H17" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="I17" s="3">
         <v>1529900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1740700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1505400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1400600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1660300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1850400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1660800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1745100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2085800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4845600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2230300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1821800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1925700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4151100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1687500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1305500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1379600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2123100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>973400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>946300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1092600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>966700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>942700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>949600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>924600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>812300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>824300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E18" s="3">
         <v>91900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>126900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>92200</v>
       </c>
-      <c r="G18" s="3">
-        <v>85600</v>
-      </c>
       <c r="H18" s="3">
+        <v>84100</v>
+      </c>
+      <c r="I18" s="3">
         <v>119500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>161300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>133600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>123700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>167300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>193500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>161700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>168600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>237100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>544600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>259000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>195000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>168100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>374400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>137500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>88200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>106600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>151000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>58700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>51700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>70400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>122600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>48400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>45500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>57000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>60600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>44300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>41500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>52300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>87700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>33800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>35300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1983,115 +2015,116 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>600</v>
       </c>
       <c r="J20" s="3">
         <v>600</v>
       </c>
       <c r="K20" s="3">
+        <v>600</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>200</v>
       </c>
       <c r="AG20" s="3">
         <v>200</v>
       </c>
       <c r="AH20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>400</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>100</v>
       </c>
       <c r="AM20" s="3">
         <v>100</v>
@@ -2099,124 +2132,130 @@
       <c r="AN20" s="3">
         <v>100</v>
       </c>
+      <c r="AO20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E21" s="3">
         <v>132800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>167700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>130900</v>
       </c>
-      <c r="G21" s="3">
-        <v>125400</v>
-      </c>
       <c r="H21" s="3">
+        <v>123900</v>
+      </c>
+      <c r="I21" s="3">
         <v>156800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>197100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>168900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>158500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>199900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>225500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>191900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>208000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>263700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>590600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>283900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>223400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>192400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>422500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>161900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>110700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>126800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>185500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>73100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>71000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>88100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>157100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>66400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>60400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>73100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>75700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>58900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>55500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>66300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>113800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>46400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>48200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2224,70 +2263,70 @@
         <v>2800</v>
       </c>
       <c r="E22" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="F22" s="3">
         <v>2700</v>
       </c>
       <c r="G22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H22" s="3">
         <v>3500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3200</v>
       </c>
       <c r="L22" s="3">
         <v>3200</v>
       </c>
       <c r="M22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N22" s="3">
         <v>3300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3300</v>
       </c>
       <c r="S22" s="3">
         <v>3300</v>
       </c>
       <c r="T22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U22" s="3">
         <v>3400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3800</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>1900</v>
       </c>
       <c r="AA22" s="3">
         <v>1900</v>
@@ -2296,275 +2335,284 @@
         <v>1900</v>
       </c>
       <c r="AC22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD22" s="3">
         <v>4900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E23" s="3">
         <v>99100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>131900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>100700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>91000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>134100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>168400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>146600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>135700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>173500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>197500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>164500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>173000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>230700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>531100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>254100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>193100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>163400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>369900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>136000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>88100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>105700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>147200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>53900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>51600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>69000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>120100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>47600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>40900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>55300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>58600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>43200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>40300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>50900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>84800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>32400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>34100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E24" s="3">
         <v>23600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>42200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>58600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>130100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>61000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>46100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>90300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>26800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>11600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>17300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>9600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>16300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>28600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>10800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>11900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2679,240 +2727,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E26" s="3">
         <v>75500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>79400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>69800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>101600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>126200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>121100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>103900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>134200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>150800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>125600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>131900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>172100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>401000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>193100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>147000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>125700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>279600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>104300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>64800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>78900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>110300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>40600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>38700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>91100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>36000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>42100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>45100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>33600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>43500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>34700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>56200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>21600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>22200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E27" s="3">
         <v>72500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>97000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>75800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>65400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>96000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>121100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>115900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>98200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>127300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>143200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>120500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>127100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>160400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>377700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>182900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>133400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>117100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>267800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>61200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>75000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>103700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>36800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>50600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>87800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>34700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>21800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>40300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>43000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>32100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>33000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>53700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>20700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>20400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3027,8 +3084,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3095,8 +3155,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3113,11 +3173,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3125,11 +3185,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3143,8 +3203,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3259,8 +3322,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3375,115 +3441,118 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-600</v>
       </c>
       <c r="J32" s="3">
         <v>-600</v>
       </c>
       <c r="K32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-200</v>
       </c>
       <c r="AG32" s="3">
         <v>-200</v>
       </c>
       <c r="AH32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-100</v>
       </c>
       <c r="AM32" s="3">
         <v>-100</v>
@@ -3491,124 +3560,130 @@
       <c r="AN32" s="3">
         <v>-100</v>
       </c>
+      <c r="AO32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E33" s="3">
         <v>75300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>78800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>68000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>99800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>120800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>103400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>134000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>150800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>126100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>127100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>160400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>377700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>182900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>133400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>117100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>267800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>61200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>75000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>103700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>36800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>50600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>87800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>34700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>29800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>40300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>43000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>32100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>33000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>53700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>20700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>20400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3723,245 +3798,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E35" s="3">
         <v>75300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>78800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>68000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>99800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>120800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>103400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>134000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>150800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>126100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>127100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>160400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>377700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>182900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>133400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>117100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>267800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>61200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>75000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>103700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>36800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>50600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>87800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>34700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>29800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>40300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>43000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>32100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>33000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>53700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>20700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>20400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44828</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44737</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44464</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44282</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44191</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4002,8 +4086,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4044,743 +4129,762 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>914200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1008600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>841900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>903600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1171800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1190800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1041300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>979700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1118300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>957100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>702100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>423300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>559400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>449100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>138100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>73800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>286700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>138600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>44300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>436500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>346200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>168300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>64500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>17100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>25300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>28300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>22000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>31000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>34100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E42" s="3">
         <v>33900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>32000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>36700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>34700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>37500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>36000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33100</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>35500</v>
       </c>
       <c r="R42" s="3">
         <v>35500</v>
       </c>
       <c r="S42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="T42" s="3">
         <v>36500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>33700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>33800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>31400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>24300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>20500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>19200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>17800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>17000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>16800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>16200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>15800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>14500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>10300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>519300</v>
+      </c>
+      <c r="E43" s="3">
         <v>614800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>715200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>723100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>529000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>699800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>759600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>722200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>582400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>725700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>819300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>814800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>657500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>915000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1066000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1102100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>748200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>801900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>984800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>811500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>480500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>587200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>527300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>469200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>382000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>483000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>489600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>456600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>364500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>469200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>497000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>432800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>422500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>398500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>368800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>293700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E44" s="3">
         <v>667400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>722200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>754900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>720800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>645400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>684800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>745300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>727800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>744700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>821200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>960300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>973200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1006900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1106300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1230400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>963300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>900700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1026500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>823400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>567300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>528700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>459400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>510700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>486900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>479400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>528700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>580200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>556200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>510100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>531900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>521700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>460300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>412500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>438400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>472000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>397200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E45" s="3">
         <v>59200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>47900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>33100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>30100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>31100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>37300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>41600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>33400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>32500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>25400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>41700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>53200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>20700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>22900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>21600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>21100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2268700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2387100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2367500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2464400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2503000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2613500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2554000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2514400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2502100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2505100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2415100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2267000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2262100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2436400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2376400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2472400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2073500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1922800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2122500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1737100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1538400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1512100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1236600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1060900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1093100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1092100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1097100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1103500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>995300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>863500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>888600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>894900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>899300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>756400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E47" s="3">
         <v>53400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>54200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>55400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>56400</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>22000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>116600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64300</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4856,240 +4960,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1108400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1099300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1076900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1039500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1005500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>967100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>944400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>923400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>880400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>845200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>823900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>816700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>796500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>745000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>733000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>700800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>685700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>647400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>630800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>586800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>494400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>483400</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>478600</v>
       </c>
       <c r="Z48" s="3">
         <v>478600</v>
       </c>
       <c r="AA48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="AB48" s="3">
         <v>467300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>460400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>439200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>422300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>354700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>346300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>340700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>313600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>328600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>325100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>316000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>309900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>297900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>484900</v>
+      </c>
+      <c r="E49" s="3">
         <v>488800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>494500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>495900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>499600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>501600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>505100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>511100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>518900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>476300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>481900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>487100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>488600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>440400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>445800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>445200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>431400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>393700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>424100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>415400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>331800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>311500</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>300000</v>
       </c>
       <c r="Z49" s="3">
         <v>300000</v>
       </c>
       <c r="AA49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>285200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>286600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>273800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>271300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>273000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>261700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>263000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>254500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>255000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>255700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>253500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>250200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>227600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5204,8 +5317,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5320,124 +5436,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E52" s="3">
         <v>101800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>99200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>90300</v>
       </c>
-      <c r="G52" s="3">
-        <v>81100</v>
-      </c>
       <c r="H52" s="3">
+        <v>137500</v>
+      </c>
+      <c r="I52" s="3">
         <v>131500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>109600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>126100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>112300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>121800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>124900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>116800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>55600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>55500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>54600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>50400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>50900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>46900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>40300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>43500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>43900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>41500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>40500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>22300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>19600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>17500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>17700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>18300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5552,124 +5674,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4022900</v>
+      </c>
+      <c r="E54" s="3">
         <v>4135600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4097400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4150300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4150900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4217900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4138500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4078600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4017800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4004100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3843900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3696800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3672100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3738500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3610800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3674000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3245300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3014200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3228300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2786100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2404900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2350600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2058600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1889500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1880600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1850700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1821400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5710,8 +5838,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5752,189 +5881,193 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>205900</v>
+      </c>
+      <c r="E57" s="3">
         <v>231900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>258800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>277700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>224700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>239900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>263300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>254900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>203100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>253100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>264400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>278000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>206900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>323400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>386800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>426000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>319100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>292900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>359500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>299400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>211500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>231100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>199300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>162000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>142500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>180800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>189600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>170700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>136900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>175900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>197400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>176500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>140100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>171800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>160300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>156000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>124700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E58" s="3">
         <v>34200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>32100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>72500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>71800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>70600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>65900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>25900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>28300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>30900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>45700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>52400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>104600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>59700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>34300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>100</v>
-      </c>
-      <c r="X58" s="3">
-        <v>2800</v>
       </c>
       <c r="Y58" s="3">
         <v>2800</v>
@@ -5946,510 +6079,525 @@
         <v>2800</v>
       </c>
       <c r="AB58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>25100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>18900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>27500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>31300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>34200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>30500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>27200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>28800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>25100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>23800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>22400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>402000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>433700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>384700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>372600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>397200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>361800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>337500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>264400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>252100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>259700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>233100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>164400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>208700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>204500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>164800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>131000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>145800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>151100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>138800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>106200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>138400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>126200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>98000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>124700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>494200</v>
+      </c>
+      <c r="E60" s="3">
         <v>532200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>521100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>496500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>512400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>606000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>588400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>525000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>568000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>601800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>556000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>530400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>611800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>802900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>824000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>903200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>776000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>665700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>731300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>611000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>463700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>493600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>435200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>329300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>354000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>385400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>379600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>320600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>310200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>358300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>370400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>313100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>303200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>339000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>311600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>277800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>271800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E61" s="3">
         <v>335100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>342000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>326200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>324900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>333800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>335900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>339300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>318400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>359900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>359000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>367200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>275200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>275400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>276300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>379000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>277600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>310100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>571900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>426300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>311600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>311300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>161100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>160600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>160900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>162900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>187500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>266400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>202100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>186500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>276300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>261300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>144700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>145900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>204800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>252900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>109100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E62" s="3">
         <v>29700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>36000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>181400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>184000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>185400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>173600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>175100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>161000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>165500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>162200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>146400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>131900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>123000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>120900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>116800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>103200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>100300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>96000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>46600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>40600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>40100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>42700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>52000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>49300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>49600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>50800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6564,8 +6712,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6680,8 +6831,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6796,124 +6950,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>934200</v>
+      </c>
+      <c r="E66" s="3">
         <v>927300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>923700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>886000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1018500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1002100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>943200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>967600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1048500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1002200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>984300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1108100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1301500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1330700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1496100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1266700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1163500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1491800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1219900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>944600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>953000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>734200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>622300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>645800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>665200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>683300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>698500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>574100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>601100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>704100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>629900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>505200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>551100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>580300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>593100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>442900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6954,8 +7114,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7070,8 +7231,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7186,8 +7350,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,8 +7469,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7418,124 +7588,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2559400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2689500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2663400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2772800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2775300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2728300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2670100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2664100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2582300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2517300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2408300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2293000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2217400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2102800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1950900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1851800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1678100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1552600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1440800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1276700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1182700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1127400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1057800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>999000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>995000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>969600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>917700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>875500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>839900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>841400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>800200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>768200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>736200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>715500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>684800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>670100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>649100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7650,8 +7826,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7766,8 +7945,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7882,124 +8064,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3062400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3180400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3145400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3237700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3224100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3174400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3096800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3087800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2999800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2919400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2803400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2675800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2564000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2437100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2280100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2177900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1978600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1850800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1736500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1566200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1460300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1397600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1324400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1260700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1243700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1215500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1167400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1122900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>959500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>935800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>901700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>884500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>849200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8114,245 +8302,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44828</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44737</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44464</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44282</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44191</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E81" s="3">
         <v>75300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>78800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>68000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>99800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>120800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>103400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>134000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>150800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>126100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>127100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>160400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>377700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>182900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>133400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>117100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>267800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>61200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>75000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>103700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>36800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>50600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>87800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>34700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>29800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>40300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>43000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>32100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>33000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>53700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>20700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>20400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8393,124 +8590,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E83" s="3">
         <v>31500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>22200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>52800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>45500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>22700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>34500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>16300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>16600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>15900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>14900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>25600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>12500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>12700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8625,8 +8826,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8741,8 +8945,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8857,8 +9064,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8973,8 +9183,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9089,124 +9302,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E89" s="3">
         <v>286000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>221900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-108800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>144900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>258600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>255900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>248100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>390700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>358100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>298500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>442600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>90400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-245000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>230700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>397500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-115700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-196700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>151400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>147200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-46200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>151200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>127100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>70900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-55800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>96200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>48100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>82100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>15200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>36100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9247,124 +9466,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-75800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-62500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-57400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-49100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-38200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-32100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-79000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9479,8 +9702,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9595,124 +9821,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-67600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-75600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-93300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-63000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-56100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-102200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-131300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-103800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-118800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-59700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-82900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-514000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-296500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-66200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-36100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-47700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9753,98 +9985,99 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E96" s="3">
         <v>20500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>20700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>21300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>20100</v>
       </c>
       <c r="H96" s="3">
         <v>20100</v>
       </c>
       <c r="I96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="J96" s="3">
         <v>20200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>20400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>18500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>18600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>15500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>15600</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-15400</v>
       </c>
       <c r="P96" s="3">
         <v>-15400</v>
       </c>
       <c r="Q96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="R96" s="3">
         <v>-28000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-12500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-9300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-18600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-7600</v>
       </c>
       <c r="X96" s="3">
         <v>-7600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -9852,25 +10085,28 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9985,8 +10221,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10101,8 +10340,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10217,352 +10459,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-178100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-211400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-90900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-61400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-49200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-127500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-69000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-29200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-59400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-58600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-125000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>86300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-271500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>237900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>101900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>142200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-39700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>61100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>111600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>74500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>141700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-86600</v>
+      </c>
+      <c r="E102" s="3">
         <v>168700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-275000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>149500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>61600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-141700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>161400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>257900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>278800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-135600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>311100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-152400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-216700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>135000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>111300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-391700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-391600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>89700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>145600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-135800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>103400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>43700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>28900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-50800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UFPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>UFPI</t>
   </si>
@@ -656,528 +656,541 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46018</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44828</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44737</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44464</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44282</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44191</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1461300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1329800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1559600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1835400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1595500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1462000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1649400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1902000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1639000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1524400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1827600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2043900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1822500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1913700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2322900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5390200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2489300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2016800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2093800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4525500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1825000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1393700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1486200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2274100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1032100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>998000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1163000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2254900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1015100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>988200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1212700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1294400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>993900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>966100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1056600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1918500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>846100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>859600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>826700</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1225400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1113300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1296900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1522600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1327300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1222500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1351000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1539200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1312900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1228200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1463200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1643900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1464100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1556200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1872700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4408400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2011000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1645200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1766200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3817700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1538500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1206700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1245200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1901900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>864800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>840800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>975800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1914000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>860900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>850500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1054000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1128800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>863000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>836900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>911900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1649500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>725400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>737300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>708600</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>235900</v>
+      </c>
+      <c r="E10" s="3">
         <v>216500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>262700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>312700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>268200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>239500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>298400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>362700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>326100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>296100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>364400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>358300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>357500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>450200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>981800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>478400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>371600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>327600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>707800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>286600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>187000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>241000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>372200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>167300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>157200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>187200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>341000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>154200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>137700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>158700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>165600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>130900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>129200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>144700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>269000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>120700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>122300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>118100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1219,8 +1232,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1338,8 +1352,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1457,40 +1474,43 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1498,8 +1518,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1576,50 +1596,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E15" s="3">
         <v>41800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>40600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>39900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>38800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>37400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30800</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1718,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1735,246 +1761,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1398800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1275800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1467700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1708500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1503300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1377900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1529900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1740700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1505400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1400600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1660300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1850400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1660800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1745100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2085800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4845600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2230300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1821800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1925700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4151100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1687500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1305500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1379600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2123100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>973400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>946300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1092600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2132300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>966700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>942700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1155700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1233800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>949600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>924600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1004300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1830800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>812300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>824300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>783100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E18" s="3">
         <v>54000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>91900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>126900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>92200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>84100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>119500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>161300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>133600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>123700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>167300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>193500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>161700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>168600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>237100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>544600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>259000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>195000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>168100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>374400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>137500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>88200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>106600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>151000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>58700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>51700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>70400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>122600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>48400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>45500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>60600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>44300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>41500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>52300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>87700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>33800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>35300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2016,118 +2049,119 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>600</v>
       </c>
       <c r="K20" s="3">
         <v>600</v>
       </c>
       <c r="L20" s="3">
+        <v>600</v>
+      </c>
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>200</v>
       </c>
       <c r="AH20" s="3">
         <v>200</v>
       </c>
       <c r="AI20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>400</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>100</v>
       </c>
       <c r="AN20" s="3">
         <v>100</v>
@@ -2135,201 +2169,207 @@
       <c r="AO20" s="3">
         <v>100</v>
       </c>
+      <c r="AP20" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E21" s="3">
         <v>95500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>132800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>167700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>130900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>123900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>156800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>197100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>168900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>158500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>199900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>225500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>191900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>208000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>263700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>590600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>283900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>223400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>192400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>422500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>161900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>110700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>126800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>185500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>73100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>71000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>88100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>157100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>66400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>60400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>73100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>75700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>58900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>55500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>66300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>113800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>46400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>48200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="E22" s="3">
         <v>2800</v>
       </c>
       <c r="F22" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G22" s="3">
         <v>2700</v>
       </c>
       <c r="H22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3200</v>
       </c>
       <c r="M22" s="3">
         <v>3200</v>
       </c>
       <c r="N22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O22" s="3">
         <v>3300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6700</v>
-      </c>
-      <c r="S22" s="3">
-        <v>3300</v>
       </c>
       <c r="T22" s="3">
         <v>3300</v>
       </c>
       <c r="U22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V22" s="3">
         <v>3400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3800</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>1900</v>
       </c>
       <c r="AB22" s="3">
         <v>1900</v>
@@ -2338,281 +2378,290 @@
         <v>1900</v>
       </c>
       <c r="AD22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E23" s="3">
         <v>60500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>99100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>131900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>91000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>134100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>168400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>146600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>135700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>173500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>197500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>164500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>173000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>230700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>531100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>254100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>193100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>163400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>369900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>136000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>88100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>105700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>147200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>53900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>51600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>69000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>120100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>47600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>40900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>55300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>58600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>40300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>50900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>84800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>32400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>34100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E24" s="3">
         <v>20300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>31100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>32500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>41200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>130100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>61000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>90300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>23300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>26800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>17300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>16300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>28600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>10800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>11900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2730,246 +2779,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E26" s="3">
         <v>40200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>75500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>100900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>79400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>69800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>126200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>121100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>103900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>134200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>150800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>125600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>131900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>172100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>401000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>193100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>147000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>125700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>279600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>104300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>64800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>78900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>110300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>40600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>38700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>52600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>91100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>36000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>42100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>45100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>33600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>43500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>34700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>56200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>21600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>22200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E27" s="3">
         <v>38400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>72500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>97000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>75800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>65400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>96000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>121100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>115900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>98200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>127300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>143200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>127100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>160400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>377700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>182900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>133400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>117100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>267800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>61200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>75000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>103700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>36800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>50600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>87800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>34700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>40300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>43000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>40800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>33000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>53700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>20700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>20400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3087,8 +3145,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3158,8 +3219,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3176,11 +3237,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3188,11 +3249,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3206,8 +3267,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3325,8 +3389,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3444,118 +3511,121 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-600</v>
       </c>
       <c r="K32" s="3">
         <v>-600</v>
       </c>
       <c r="L32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-200</v>
       </c>
       <c r="AH32" s="3">
         <v>-200</v>
       </c>
       <c r="AI32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>-100</v>
       </c>
       <c r="AN32" s="3">
         <v>-100</v>
@@ -3563,127 +3633,133 @@
       <c r="AO32" s="3">
         <v>-100</v>
       </c>
+      <c r="AP32" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E33" s="3">
         <v>40000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>75300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>100700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>78800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>68000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>99800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>120800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>103400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>134000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>150800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>126100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>127100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>160400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>377700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>182900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>133400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>117100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>267800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>61200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>75000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>103700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>36800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>50600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>87800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>34700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>29800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>40300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>43000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>30500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>33000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>53700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>20700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>20400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3801,251 +3877,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E35" s="3">
         <v>40000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>75300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>100700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>78800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>68000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>99800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>120800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>103400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>134000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>150800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>126100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>127100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>160400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>377700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>182900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>133400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>117100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>267800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>61200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>75000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>103700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>36800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>50600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>87800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>34700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>29800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>40300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>43000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>30500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>33000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>53700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>20700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>20400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46018</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44828</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44737</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44464</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44282</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44191</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4087,8 +4172,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4130,764 +4216,783 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>714500</v>
+      </c>
+      <c r="E41" s="3">
         <v>914200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1008600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>841900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>903600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1171800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1190800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1041300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>979700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1118300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>957100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>702100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>423300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>559400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>449100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>138100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>73800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>286700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>138600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>44300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>44400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>436500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>346200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>200500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>168300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>64500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>17100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>26300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>27500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>28300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>22000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>31000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>34100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>36700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E42" s="3">
         <v>34400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>33900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>30700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>36700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>34700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>37100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>37500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>36000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33100</v>
-      </c>
-      <c r="R42" s="3">
-        <v>35500</v>
       </c>
       <c r="S42" s="3">
         <v>35500</v>
       </c>
       <c r="T42" s="3">
+        <v>35500</v>
+      </c>
+      <c r="U42" s="3">
         <v>36500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>33700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>33800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>31400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>24300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>18500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>16800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>16200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>14800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>15800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>14500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>11300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>10400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>10300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>674200</v>
+      </c>
+      <c r="E43" s="3">
         <v>519300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>614800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>715200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>723100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>529000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>699800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>759600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>722200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>582400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>725700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>819300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>814800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>657500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>915000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1066000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1102100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>748200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>801900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>984800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>811500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>480500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>587200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>527300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>469200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>382000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>483000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>489600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>456600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>364500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>469200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>497000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>432800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>335000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>422500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>398500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>368800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>293700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>351200</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>767100</v>
+      </c>
+      <c r="E44" s="3">
         <v>722000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>667400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>722200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>754900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>720800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>645400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>684800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>745300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>727800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>744700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>821200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>960300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>973200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1006900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1106300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1230400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>963300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>900700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1026500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>823400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>567300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>528700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>459400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>510700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>486900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>479400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>528700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>580200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>556200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>510100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>531900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>521700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>460300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>412500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>438400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>472000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>397200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>369900</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E45" s="3">
         <v>67900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>59200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>55100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>47900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>33100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>26300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>31100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>37300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>48200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>41600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>32500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>25400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>41700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>53200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>28600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>20700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>22900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>21600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>21100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2269700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2268700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2387100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2367500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2464400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2503000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2613500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2554000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2514400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2502100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2505100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2415100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2267000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2262100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2436400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2376400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2472400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2073500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1922800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2122500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1737100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1538400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1512100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1236600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1060900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1093100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1092100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1097100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1103500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>995300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1046900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1112600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1043700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>863500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>888600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>894900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>899300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>756400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>790800</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E47" s="3">
         <v>52700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>53400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>55400</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>22000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>116600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>64300</v>
       </c>
-      <c r="O47" s="3" t="s">
+      <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4963,246 +5068,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1123400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1108400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1099300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1076900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1039500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1005500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>967100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>944400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>923400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>880400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>845200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>823900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>816700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>796500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>745000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>733000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>700800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>685700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>647400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>630800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>586800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>494400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>483400</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>478600</v>
       </c>
       <c r="AA48" s="3">
         <v>478600</v>
       </c>
       <c r="AB48" s="3">
+        <v>478600</v>
+      </c>
+      <c r="AC48" s="3">
         <v>467300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>460400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>439200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>422300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>354700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>346300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>340700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>313600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>328600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>325100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>316000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>309900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>297900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>284500</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>478800</v>
+      </c>
+      <c r="E49" s="3">
         <v>484900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>488800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>494500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>495900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>499600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>501600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>505100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>511100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>518900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>476300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>481900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>487100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>488600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>440400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>445800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>445200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>431400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>393700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>424100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>415400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>331800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>311500</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>300000</v>
       </c>
       <c r="AA49" s="3">
         <v>300000</v>
       </c>
       <c r="AB49" s="3">
+        <v>300000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>285200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>286600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>273800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>271300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>273000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>261700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>263000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>254500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>255000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>255700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>253500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>250200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>227600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>224200</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5320,8 +5434,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5439,127 +5556,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E52" s="3">
         <v>100300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>101800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>99200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>90300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>137500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>131500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>109600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>126100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>112300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>121800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>124900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>116800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>55600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>55500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>54600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>50400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>50900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>40300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>43400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>43500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>43900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>41500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>40500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>20300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>19600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>17600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>17500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>17700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>18300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>10200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5677,127 +5800,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4031800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4022900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4135600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4097400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4150300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4150900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4217900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4138500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4078600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4017800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4004100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3843900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3696800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3672100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3738500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3610800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3674000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3245300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3014200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3228300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2786100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2404900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2350600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2058600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1889500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1880600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1850700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1821400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1647500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1677200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1736600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1631500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1464700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1486900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1482000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1477700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1292100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1310600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5839,8 +5968,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5882,195 +6012,199 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E57" s="3">
         <v>205900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>231900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>258800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>277700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>224700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>239900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>263300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>254900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>203100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>253100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>264400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>278000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>206900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>323400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>386800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>426000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>319100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>292900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>359500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>299400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>211500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>231100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>199300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>162000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>142500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>180800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>189600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>170700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>136900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>175900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>197400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>176500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>140100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>171800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>160300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>156000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>124700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E58" s="3">
         <v>28900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>32000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>71800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>70600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>65900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>30900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>45700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>52400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>104600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>59700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>34300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>47200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>100</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>2800</v>
       </c>
       <c r="Z58" s="3">
         <v>2800</v>
@@ -6082,522 +6216,537 @@
         <v>2800</v>
       </c>
       <c r="AC58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AD58" s="3">
         <v>200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>25100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>27500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>31300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>34200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>27200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>28800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>25100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>23800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>22400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>402000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>433700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>384700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>372600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>397200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>361800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>337500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>264400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>252100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>259700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>233100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>164400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>208700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>204500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>164800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>131000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>145800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>151100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>138800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>106200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>136000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>138400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>126200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>98000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>124700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>488900</v>
+      </c>
+      <c r="E60" s="3">
         <v>494200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>532200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>521100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>496500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>512400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>606000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>588400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>525000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>568000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>601800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>556000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>530400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>611800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>802900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>824000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>903200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>776000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>665700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>731300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>611000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>463700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>493600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>435200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>329300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>354000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>385400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>379600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>320600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>310200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>358300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>370400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>313100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>303200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>339000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>311600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>277800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>271800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>310200</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E61" s="3">
         <v>327900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>335100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>342000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>326200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>324900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>333800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>335900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>339300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>318400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>359900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>359000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>367200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>275200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>275400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>276300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>379000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>277600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>310100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>571900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>426300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>311600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>311300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>161100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>160600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>160900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>162900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>187500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>266400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>202100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>186500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>276300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>261300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>144700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>145900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>204800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>252900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>109100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>29700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>36100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>35600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>181400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>184000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>185400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>173600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>175100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>161000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>165500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>162200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>146400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>131900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>123000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>120900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>116800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>103200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>100300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>96000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>40600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>42300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>42700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>52000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>49300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>49600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>50800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6715,8 +6864,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6834,8 +6986,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6953,127 +7108,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>930600</v>
+      </c>
+      <c r="E66" s="3">
         <v>934200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>927300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>923700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>886000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1018500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1002100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>943200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>967600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1048500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1002200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>984300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1108100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1301500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1330700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1496100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1266700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1163500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1491800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1219900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>944600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>953000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>734200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>622300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>645800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>665200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>683300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>698500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>574100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>601100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>704100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>629900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>505200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>551100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>580300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>593100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>442900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>473700</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7115,8 +7276,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7234,8 +7396,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7353,8 +7518,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7472,8 +7640,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7591,127 +7762,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2561200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2559400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2689500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2663400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2772800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2775300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2728300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2670100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2664100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2582300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2517300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2408300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2293000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2217400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2102800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1950900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1851800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1678100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1552600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1440800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1276700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1182700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1127400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1057800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>999000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>995000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>969600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>917700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>875500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>839900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>841400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>800200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>768200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>736200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>715500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>684800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>670100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>649100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7829,8 +8006,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7948,8 +8128,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8067,127 +8250,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3079600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3062400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3180400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3145400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3237700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3224100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3174400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3096800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3087800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2999800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2919400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2803400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2675800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2564000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2437100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2280100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2177900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1978600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1850800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1736500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1566200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1460300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1397600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1324400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1260700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1243700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1215500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1167400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1122900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1073400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1076100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1032500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>959500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>935800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>901700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>884500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>849200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>837000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8305,251 +8494,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46018</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44828</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44737</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44464</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44282</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44191</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E81" s="3">
         <v>40000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>75300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>100700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>78800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>68000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>99800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>120800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>103400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>134000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>150800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>126100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>127100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>160400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>377700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>182900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>133400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>117100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>267800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>61200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>75000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>103700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>36800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>50600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>87800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>34700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>29800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>40300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>43000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>30500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>33000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>53700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>20700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>20400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8591,127 +8789,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E83" s="3">
         <v>32500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>22200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>52800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>45500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>22700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>34500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>16300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>15900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>14900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>13900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>25600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>12500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>12700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8829,8 +9031,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8948,8 +9153,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9067,8 +9275,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9186,8 +9397,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9305,127 +9519,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-103600</v>
+      </c>
+      <c r="E89" s="3">
         <v>146600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>286000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>221900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-108800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>144900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>258600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>255900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>248100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>390700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>358100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>298500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>442600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>90400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-245000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>230700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>397500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-115700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-196700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>151400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>147200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>151200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>127100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>70900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-55800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>96200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>48100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-84200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>82100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>15200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-70700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>36100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>96300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9467,127 +9687,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-75800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-67300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-57400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-46800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-38200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-39600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-31100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-79000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-42500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9705,8 +9929,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9824,127 +10051,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-67600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-74000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-75600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-93300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-102200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-131300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-103800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-118800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-59700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-82900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-514000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-296500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-53800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-34700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-66200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-36100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-58200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-47700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-64400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-21500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-70600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-170800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9986,101 +10219,102 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E96" s="3">
         <v>19900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>20500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>20700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>21300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>20100</v>
       </c>
       <c r="I96" s="3">
         <v>20100</v>
       </c>
       <c r="J96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K96" s="3">
         <v>20200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>20400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>18500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>18600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>15500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>15600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-15400</v>
       </c>
       <c r="Q96" s="3">
         <v>-15400</v>
       </c>
       <c r="R96" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="S96" s="3">
         <v>-28000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-9300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-18600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-9300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-7600</v>
       </c>
       <c r="Y96" s="3">
         <v>-7600</v>
       </c>
       <c r="Z96" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -10088,25 +10322,28 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-10400</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-9200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10224,8 +10461,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10343,8 +10583,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10462,361 +10705,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-178100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-49700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-211400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-90900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-61400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-49200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-127500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-69000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-59400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-58600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-26600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-125000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>86300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-271500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>237900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>101900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>142200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-39700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>61100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-91000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>111600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-63300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>74500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>141700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-10800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-196700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-86600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>168700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-61600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-275000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>149500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-141700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>161400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>257900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>278800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-135600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>109800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>311100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-152400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-216700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>135000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>111300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-391700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-391600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>89700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>145600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>32600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-135800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>103400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>43700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-50800</v>
       </c>
     </row>
